--- a/baza_balkany.xlsx
+++ b/baza_balkany.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:I283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>Poziom_Cen_NUTS0</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Wody_Doskonała_Jakość_NUTS0</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -497,6 +502,9 @@
       <c r="H2" t="n">
         <v>49.4</v>
       </c>
+      <c r="I2" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -525,6 +533,9 @@
       <c r="H3" t="n">
         <v>49.4</v>
       </c>
+      <c r="I3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,6 +564,9 @@
       <c r="H4" t="n">
         <v>49.4</v>
       </c>
+      <c r="I4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,6 +595,9 @@
       <c r="H5" t="n">
         <v>47.6</v>
       </c>
+      <c r="I5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +626,9 @@
       <c r="H6" t="n">
         <v>47.6</v>
       </c>
+      <c r="I6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -639,6 +659,9 @@
       <c r="H7" t="n">
         <v>47.6</v>
       </c>
+      <c r="I7" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -669,6 +692,9 @@
       <c r="H8" t="n">
         <v>47.6</v>
       </c>
+      <c r="I8" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -699,6 +725,9 @@
       <c r="H9" t="n">
         <v>47.6</v>
       </c>
+      <c r="I9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -727,6 +756,9 @@
       <c r="H10" t="n">
         <v>47.6</v>
       </c>
+      <c r="I10" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -757,6 +789,9 @@
       <c r="H11" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I11" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -787,6 +822,9 @@
       <c r="H12" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I12" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -817,6 +855,9 @@
       <c r="H13" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I13" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -847,6 +888,9 @@
       <c r="H14" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I14" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -877,6 +921,9 @@
       <c r="H15" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I15" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -907,6 +954,9 @@
       <c r="H16" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I16" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -937,6 +987,9 @@
       <c r="H17" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I17" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -967,6 +1020,9 @@
       <c r="H18" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I18" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -997,6 +1053,9 @@
       <c r="H19" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I19" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1027,6 +1086,9 @@
       <c r="H20" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I20" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1057,6 +1119,9 @@
       <c r="H21" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I21" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1087,6 +1152,9 @@
       <c r="H22" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I22" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1117,6 +1185,9 @@
       <c r="H23" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="I23" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1145,6 +1216,9 @@
       <c r="H24" t="n">
         <v>66.3</v>
       </c>
+      <c r="I24" t="n">
+        <v>981</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1175,6 +1249,9 @@
       <c r="H25" t="n">
         <v>66.3</v>
       </c>
+      <c r="I25" t="n">
+        <v>981</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1203,6 +1280,9 @@
       <c r="H26" t="n">
         <v>66.3</v>
       </c>
+      <c r="I26" t="n">
+        <v>981</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1231,6 +1311,9 @@
       <c r="H27" t="n">
         <v>66.3</v>
       </c>
+      <c r="I27" t="n">
+        <v>981</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1261,6 +1344,9 @@
       <c r="H28" t="n">
         <v>66.3</v>
       </c>
+      <c r="I28" t="n">
+        <v>981</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1291,6 +1377,7 @@
       <c r="H29" t="n">
         <v>44.9</v>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1408,9 @@
       <c r="H30" t="n">
         <v>50.4</v>
       </c>
+      <c r="I30" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1351,6 +1441,9 @@
       <c r="H31" t="n">
         <v>50.4</v>
       </c>
+      <c r="I31" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1381,6 +1474,9 @@
       <c r="H32" t="n">
         <v>50.4</v>
       </c>
+      <c r="I32" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1409,6 +1505,9 @@
       <c r="H33" t="n">
         <v>50.4</v>
       </c>
+      <c r="I33" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1536,9 @@
       <c r="H34" t="n">
         <v>50.4</v>
       </c>
+      <c r="I34" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1467,6 +1569,9 @@
       <c r="H35" t="n">
         <v>50.4</v>
       </c>
+      <c r="I35" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1497,6 +1602,9 @@
       <c r="H36" t="n">
         <v>50.4</v>
       </c>
+      <c r="I36" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1527,6 +1635,9 @@
       <c r="H37" t="n">
         <v>50.4</v>
       </c>
+      <c r="I37" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1555,6 +1666,9 @@
       <c r="H38" t="n">
         <v>51.7</v>
       </c>
+      <c r="I38" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1583,6 +1697,9 @@
       <c r="H39" t="n">
         <v>51.7</v>
       </c>
+      <c r="I39" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1728,9 @@
       <c r="H40" t="n">
         <v>51.7</v>
       </c>
+      <c r="I40" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1639,6 +1759,9 @@
       <c r="H41" t="n">
         <v>49.4</v>
       </c>
+      <c r="I41" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1667,6 +1790,9 @@
       <c r="H42" t="n">
         <v>49.4</v>
       </c>
+      <c r="I42" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1697,6 +1823,9 @@
       <c r="H43" t="n">
         <v>49.4</v>
       </c>
+      <c r="I43" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1856,9 @@
       <c r="H44" t="n">
         <v>49.4</v>
       </c>
+      <c r="I44" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1757,6 +1889,9 @@
       <c r="H45" t="n">
         <v>49.4</v>
       </c>
+      <c r="I45" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1920,9 @@
       <c r="H46" t="n">
         <v>49.4</v>
       </c>
+      <c r="I46" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1815,6 +1953,9 @@
       <c r="H47" t="n">
         <v>84.8</v>
       </c>
+      <c r="I47" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1845,6 +1986,9 @@
       <c r="H48" t="n">
         <v>84.8</v>
       </c>
+      <c r="I48" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1875,6 +2019,9 @@
       <c r="H49" t="n">
         <v>84.8</v>
       </c>
+      <c r="I49" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1905,6 +2052,9 @@
       <c r="H50" t="n">
         <v>84.8</v>
       </c>
+      <c r="I50" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1935,6 +2085,9 @@
       <c r="H51" t="n">
         <v>84.8</v>
       </c>
+      <c r="I51" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1965,6 +2118,9 @@
       <c r="H52" t="n">
         <v>84.8</v>
       </c>
+      <c r="I52" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1995,6 +2151,9 @@
       <c r="H53" t="n">
         <v>84.8</v>
       </c>
+      <c r="I53" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2025,6 +2184,9 @@
       <c r="H54" t="n">
         <v>84.8</v>
       </c>
+      <c r="I54" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2055,6 +2217,9 @@
       <c r="H55" t="n">
         <v>84.8</v>
       </c>
+      <c r="I55" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2085,6 +2250,9 @@
       <c r="H56" t="n">
         <v>84.8</v>
       </c>
+      <c r="I56" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2115,6 +2283,9 @@
       <c r="H57" t="n">
         <v>84.8</v>
       </c>
+      <c r="I57" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2145,6 +2316,9 @@
       <c r="H58" t="n">
         <v>84.8</v>
       </c>
+      <c r="I58" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2175,6 +2349,9 @@
       <c r="H59" t="n">
         <v>84.8</v>
       </c>
+      <c r="I59" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2203,6 +2380,9 @@
       <c r="H60" t="n">
         <v>67</v>
       </c>
+      <c r="I60" t="n">
+        <v>953</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2233,6 +2413,9 @@
       <c r="H61" t="n">
         <v>67</v>
       </c>
+      <c r="I61" t="n">
+        <v>953</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2261,6 +2444,9 @@
       <c r="H62" t="n">
         <v>67</v>
       </c>
+      <c r="I62" t="n">
+        <v>953</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2289,6 +2475,9 @@
       <c r="H63" t="n">
         <v>67</v>
       </c>
+      <c r="I63" t="n">
+        <v>953</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2319,6 +2508,9 @@
       <c r="H64" t="n">
         <v>67</v>
       </c>
+      <c r="I64" t="n">
+        <v>953</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2349,6 +2541,7 @@
       <c r="H65" t="n">
         <v>45.3</v>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2379,6 +2572,9 @@
       <c r="H66" t="n">
         <v>50.4</v>
       </c>
+      <c r="I66" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2409,6 +2605,9 @@
       <c r="H67" t="n">
         <v>50.4</v>
       </c>
+      <c r="I67" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2439,6 +2638,9 @@
       <c r="H68" t="n">
         <v>50.4</v>
       </c>
+      <c r="I68" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2469,6 +2671,9 @@
       <c r="H69" t="n">
         <v>50.4</v>
       </c>
+      <c r="I69" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2497,6 +2702,9 @@
       <c r="H70" t="n">
         <v>50.4</v>
       </c>
+      <c r="I70" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2527,6 +2735,9 @@
       <c r="H71" t="n">
         <v>50.4</v>
       </c>
+      <c r="I71" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2557,6 +2768,9 @@
       <c r="H72" t="n">
         <v>50.4</v>
       </c>
+      <c r="I72" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2587,6 +2801,9 @@
       <c r="H73" t="n">
         <v>50.4</v>
       </c>
+      <c r="I73" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2615,6 +2832,9 @@
       <c r="H74" t="n">
         <v>86.40000000000001</v>
       </c>
+      <c r="I74" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2645,6 +2865,9 @@
       <c r="H75" t="n">
         <v>86.40000000000001</v>
       </c>
+      <c r="I75" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2673,6 +2896,9 @@
       <c r="H76" t="n">
         <v>52.5</v>
       </c>
+      <c r="I76" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2701,6 +2927,9 @@
       <c r="H77" t="n">
         <v>52.5</v>
       </c>
+      <c r="I77" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2729,6 +2958,9 @@
       <c r="H78" t="n">
         <v>52.5</v>
       </c>
+      <c r="I78" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2757,6 +2989,9 @@
       <c r="H79" t="n">
         <v>51.3</v>
       </c>
+      <c r="I79" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2785,6 +3020,9 @@
       <c r="H80" t="n">
         <v>51.3</v>
       </c>
+      <c r="I80" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2815,6 +3053,9 @@
       <c r="H81" t="n">
         <v>51.3</v>
       </c>
+      <c r="I81" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2845,6 +3086,9 @@
       <c r="H82" t="n">
         <v>51.3</v>
       </c>
+      <c r="I82" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2875,6 +3119,9 @@
       <c r="H83" t="n">
         <v>51.3</v>
       </c>
+      <c r="I83" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2903,6 +3150,9 @@
       <c r="H84" t="n">
         <v>51.3</v>
       </c>
+      <c r="I84" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2933,6 +3183,9 @@
       <c r="H85" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I85" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2963,6 +3216,9 @@
       <c r="H86" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I86" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2993,6 +3249,9 @@
       <c r="H87" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I87" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3023,6 +3282,9 @@
       <c r="H88" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I88" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3053,6 +3315,9 @@
       <c r="H89" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I89" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3083,6 +3348,9 @@
       <c r="H90" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I90" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3113,6 +3381,9 @@
       <c r="H91" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I91" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3143,6 +3414,9 @@
       <c r="H92" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I92" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3173,6 +3447,9 @@
       <c r="H93" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I93" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3203,6 +3480,9 @@
       <c r="H94" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I94" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3233,6 +3513,9 @@
       <c r="H95" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I95" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3263,6 +3546,9 @@
       <c r="H96" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I96" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3293,6 +3579,9 @@
       <c r="H97" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="I97" t="n">
+        <v>1631</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3321,6 +3610,9 @@
       <c r="H98" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="I98" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3351,6 +3643,9 @@
       <c r="H99" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="I99" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3379,6 +3674,9 @@
       <c r="H100" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="I100" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3409,6 +3707,9 @@
       <c r="H101" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="I101" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3439,6 +3740,7 @@
       <c r="H102" t="n">
         <v>46.3</v>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3469,6 +3771,9 @@
       <c r="H103" t="n">
         <v>49.4</v>
       </c>
+      <c r="I103" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3499,6 +3804,9 @@
       <c r="H104" t="n">
         <v>49.4</v>
       </c>
+      <c r="I104" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3529,6 +3837,9 @@
       <c r="H105" t="n">
         <v>49.4</v>
       </c>
+      <c r="I105" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3557,6 +3868,9 @@
       <c r="H106" t="n">
         <v>49.4</v>
       </c>
+      <c r="I106" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3585,6 +3899,9 @@
       <c r="H107" t="n">
         <v>49.4</v>
       </c>
+      <c r="I107" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3615,6 +3932,9 @@
       <c r="H108" t="n">
         <v>49.4</v>
       </c>
+      <c r="I108" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3645,6 +3965,9 @@
       <c r="H109" t="n">
         <v>49.4</v>
       </c>
+      <c r="I109" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3674,6 +3997,9 @@
       </c>
       <c r="H110" t="n">
         <v>49.4</v>
+      </c>
+      <c r="I110" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="111">
@@ -3703,6 +4029,7 @@
       <c r="H111" t="n">
         <v>52.1</v>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3729,6 +4056,7 @@
       <c r="H112" t="n">
         <v>52.1</v>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3755,6 +4083,7 @@
       <c r="H113" t="n">
         <v>52.1</v>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3783,6 +4112,7 @@
       <c r="H114" t="n">
         <v>52.1</v>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3809,6 +4139,9 @@
       <c r="H115" t="n">
         <v>86.3</v>
       </c>
+      <c r="I115" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3837,6 +4170,9 @@
       <c r="H116" t="n">
         <v>86.3</v>
       </c>
+      <c r="I116" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3865,6 +4201,9 @@
       <c r="H117" t="n">
         <v>54.2</v>
       </c>
+      <c r="I117" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3893,6 +4232,9 @@
       <c r="H118" t="n">
         <v>54.2</v>
       </c>
+      <c r="I118" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3921,6 +4263,9 @@
       <c r="H119" t="n">
         <v>54.2</v>
       </c>
+      <c r="I119" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3949,6 +4294,9 @@
       <c r="H120" t="n">
         <v>51.6</v>
       </c>
+      <c r="I120" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3977,6 +4325,9 @@
       <c r="H121" t="n">
         <v>51.6</v>
       </c>
+      <c r="I121" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4007,6 +4358,9 @@
       <c r="H122" t="n">
         <v>51.6</v>
       </c>
+      <c r="I122" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4037,6 +4391,9 @@
       <c r="H123" t="n">
         <v>51.6</v>
       </c>
+      <c r="I123" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4067,6 +4424,9 @@
       <c r="H124" t="n">
         <v>51.6</v>
       </c>
+      <c r="I124" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4095,6 +4455,9 @@
       <c r="H125" t="n">
         <v>51.6</v>
       </c>
+      <c r="I125" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4125,6 +4488,9 @@
       <c r="H126" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I126" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4155,6 +4521,9 @@
       <c r="H127" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I127" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4185,6 +4554,9 @@
       <c r="H128" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I128" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4215,6 +4587,9 @@
       <c r="H129" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I129" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4245,6 +4620,9 @@
       <c r="H130" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I130" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4275,6 +4653,9 @@
       <c r="H131" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I131" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4305,6 +4686,9 @@
       <c r="H132" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I132" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4335,6 +4719,9 @@
       <c r="H133" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I133" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4365,6 +4752,9 @@
       <c r="H134" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I134" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4395,6 +4785,9 @@
       <c r="H135" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I135" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4425,6 +4818,9 @@
       <c r="H136" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I136" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4455,6 +4851,9 @@
       <c r="H137" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I137" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4485,6 +4884,9 @@
       <c r="H138" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="I138" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4513,6 +4915,9 @@
       <c r="H139" t="n">
         <v>65.2</v>
       </c>
+      <c r="I139" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4543,6 +4948,9 @@
       <c r="H140" t="n">
         <v>65.2</v>
       </c>
+      <c r="I140" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4571,6 +4979,9 @@
       <c r="H141" t="n">
         <v>65.2</v>
       </c>
+      <c r="I141" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4601,6 +5012,9 @@
       <c r="H142" t="n">
         <v>65.2</v>
       </c>
+      <c r="I142" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4631,6 +5045,7 @@
       <c r="H143" t="n">
         <v>44.6</v>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4661,6 +5076,9 @@
       <c r="H144" t="n">
         <v>49.7</v>
       </c>
+      <c r="I144" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4691,6 +5109,9 @@
       <c r="H145" t="n">
         <v>49.7</v>
       </c>
+      <c r="I145" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4721,6 +5142,9 @@
       <c r="H146" t="n">
         <v>49.7</v>
       </c>
+      <c r="I146" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4751,6 +5175,9 @@
       <c r="H147" t="n">
         <v>49.7</v>
       </c>
+      <c r="I147" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4779,6 +5206,9 @@
       <c r="H148" t="n">
         <v>49.7</v>
       </c>
+      <c r="I148" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4809,6 +5239,9 @@
       <c r="H149" t="n">
         <v>49.7</v>
       </c>
+      <c r="I149" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4839,6 +5272,9 @@
       <c r="H150" t="n">
         <v>49.7</v>
       </c>
+      <c r="I150" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4869,6 +5305,9 @@
       <c r="H151" t="n">
         <v>49.7</v>
       </c>
+      <c r="I151" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4899,6 +5338,7 @@
       <c r="H152" t="n">
         <v>54</v>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4927,6 +5367,7 @@
       <c r="H153" t="n">
         <v>54</v>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4955,6 +5396,7 @@
       <c r="H154" t="n">
         <v>54</v>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4985,6 +5427,7 @@
       <c r="H155" t="n">
         <v>54</v>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5013,6 +5456,9 @@
       <c r="H156" t="n">
         <v>87.2</v>
       </c>
+      <c r="I156" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5043,6 +5489,9 @@
       <c r="H157" t="n">
         <v>87.2</v>
       </c>
+      <c r="I157" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5071,6 +5520,9 @@
       <c r="H158" t="n">
         <v>54.6</v>
       </c>
+      <c r="I158" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5099,6 +5551,9 @@
       <c r="H159" t="n">
         <v>54.6</v>
       </c>
+      <c r="I159" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5127,6 +5582,9 @@
       <c r="H160" t="n">
         <v>54.6</v>
       </c>
+      <c r="I160" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5155,6 +5613,9 @@
       <c r="H161" t="n">
         <v>54.3</v>
       </c>
+      <c r="I161" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5183,6 +5644,9 @@
       <c r="H162" t="n">
         <v>54.3</v>
       </c>
+      <c r="I162" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5213,6 +5677,9 @@
       <c r="H163" t="n">
         <v>54.3</v>
       </c>
+      <c r="I163" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5243,6 +5710,9 @@
       <c r="H164" t="n">
         <v>54.3</v>
       </c>
+      <c r="I164" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5273,6 +5743,9 @@
       <c r="H165" t="n">
         <v>54.3</v>
       </c>
+      <c r="I165" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5301,6 +5774,9 @@
       <c r="H166" t="n">
         <v>54.3</v>
       </c>
+      <c r="I166" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5331,6 +5807,9 @@
       <c r="H167" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I167" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5361,6 +5840,9 @@
       <c r="H168" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I168" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5391,6 +5873,9 @@
       <c r="H169" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I169" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5421,6 +5906,9 @@
       <c r="H170" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I170" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5451,6 +5939,9 @@
       <c r="H171" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I171" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5481,6 +5972,9 @@
       <c r="H172" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I172" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5511,6 +6005,9 @@
       <c r="H173" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I173" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5541,6 +6038,9 @@
       <c r="H174" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I174" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5571,6 +6071,9 @@
       <c r="H175" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I175" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5601,6 +6104,9 @@
       <c r="H176" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I176" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5631,6 +6137,9 @@
       <c r="H177" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I177" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5661,6 +6170,9 @@
       <c r="H178" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I178" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5691,6 +6203,9 @@
       <c r="H179" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="I179" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5719,6 +6234,9 @@
       <c r="H180" t="n">
         <v>68.5</v>
       </c>
+      <c r="I180" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5749,6 +6267,9 @@
       <c r="H181" t="n">
         <v>68.5</v>
       </c>
+      <c r="I181" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5777,6 +6298,9 @@
       <c r="H182" t="n">
         <v>68.5</v>
       </c>
+      <c r="I182" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5807,6 +6331,9 @@
       <c r="H183" t="n">
         <v>68.5</v>
       </c>
+      <c r="I183" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5837,6 +6364,7 @@
       <c r="H184" t="n">
         <v>55.8</v>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5867,6 +6395,7 @@
       <c r="H185" t="n">
         <v>47.2</v>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5897,6 +6426,9 @@
       <c r="H186" t="n">
         <v>53.2</v>
       </c>
+      <c r="I186" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5927,6 +6459,9 @@
       <c r="H187" t="n">
         <v>53.2</v>
       </c>
+      <c r="I187" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5957,6 +6492,9 @@
       <c r="H188" t="n">
         <v>53.2</v>
       </c>
+      <c r="I188" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5985,6 +6523,9 @@
       <c r="H189" t="n">
         <v>53.2</v>
       </c>
+      <c r="I189" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6013,6 +6554,9 @@
       <c r="H190" t="n">
         <v>53.2</v>
       </c>
+      <c r="I190" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6043,6 +6587,9 @@
       <c r="H191" t="n">
         <v>53.2</v>
       </c>
+      <c r="I191" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6073,6 +6620,9 @@
       <c r="H192" t="n">
         <v>53.2</v>
       </c>
+      <c r="I192" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6103,6 +6653,9 @@
       <c r="H193" t="n">
         <v>53.2</v>
       </c>
+      <c r="I193" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6133,6 +6686,7 @@
       <c r="H194" t="n">
         <v>57</v>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6161,6 +6715,7 @@
       <c r="H195" t="n">
         <v>57</v>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6189,6 +6744,7 @@
       <c r="H196" t="n">
         <v>57</v>
       </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6219,6 +6775,7 @@
       <c r="H197" t="n">
         <v>57</v>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6247,6 +6804,9 @@
       <c r="H198" t="n">
         <v>87.8</v>
       </c>
+      <c r="I198" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6277,6 +6837,9 @@
       <c r="H199" t="n">
         <v>87.8</v>
       </c>
+      <c r="I199" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6304,6 +6867,9 @@
       </c>
       <c r="H200" t="n">
         <v>58.2</v>
+      </c>
+      <c r="I200" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="201">
@@ -6331,6 +6897,9 @@
       <c r="H201" t="n">
         <v>58.2</v>
       </c>
+      <c r="I201" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6358,6 +6927,9 @@
       </c>
       <c r="H202" t="n">
         <v>58.2</v>
+      </c>
+      <c r="I202" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="203">
@@ -6385,6 +6957,9 @@
       <c r="H203" t="n">
         <v>55.8</v>
       </c>
+      <c r="I203" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6411,6 +6986,9 @@
       <c r="H204" t="n">
         <v>55.8</v>
       </c>
+      <c r="I204" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6441,6 +7019,9 @@
       <c r="H205" t="n">
         <v>55.8</v>
       </c>
+      <c r="I205" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6471,6 +7052,9 @@
       <c r="H206" t="n">
         <v>55.8</v>
       </c>
+      <c r="I206" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6501,6 +7085,9 @@
       <c r="H207" t="n">
         <v>55.8</v>
       </c>
+      <c r="I207" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6529,6 +7116,9 @@
       <c r="H208" t="n">
         <v>55.8</v>
       </c>
+      <c r="I208" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6559,6 +7149,9 @@
       <c r="H209" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I209" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6589,6 +7182,9 @@
       <c r="H210" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I210" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6619,6 +7215,9 @@
       <c r="H211" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I211" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6649,6 +7248,9 @@
       <c r="H212" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I212" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6679,6 +7281,9 @@
       <c r="H213" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I213" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6709,6 +7314,9 @@
       <c r="H214" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I214" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6739,6 +7347,9 @@
       <c r="H215" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I215" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6769,6 +7380,9 @@
       <c r="H216" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I216" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6799,6 +7413,9 @@
       <c r="H217" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I217" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6829,6 +7446,9 @@
       <c r="H218" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I218" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6859,6 +7479,9 @@
       <c r="H219" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I219" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6889,6 +7512,9 @@
       <c r="H220" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I220" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6919,6 +7545,9 @@
       <c r="H221" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="I221" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6947,6 +7576,9 @@
       <c r="H222" t="n">
         <v>71.2</v>
       </c>
+      <c r="I222" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6977,6 +7609,9 @@
       <c r="H223" t="n">
         <v>71.2</v>
       </c>
+      <c r="I223" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7005,6 +7640,9 @@
       <c r="H224" t="n">
         <v>71.2</v>
       </c>
+      <c r="I224" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7035,6 +7673,9 @@
       <c r="H225" t="n">
         <v>71.2</v>
       </c>
+      <c r="I225" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7065,6 +7706,7 @@
       <c r="H226" t="n">
         <v>56.8</v>
       </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7095,6 +7737,7 @@
       <c r="H227" t="n">
         <v>48.7</v>
       </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7125,6 +7768,9 @@
       <c r="H228" t="n">
         <v>54.7</v>
       </c>
+      <c r="I228" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7155,6 +7801,9 @@
       <c r="H229" t="n">
         <v>54.7</v>
       </c>
+      <c r="I229" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7185,6 +7834,9 @@
       <c r="H230" t="n">
         <v>54.7</v>
       </c>
+      <c r="I230" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7213,6 +7865,9 @@
       <c r="H231" t="n">
         <v>54.7</v>
       </c>
+      <c r="I231" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7241,6 +7896,9 @@
       <c r="H232" t="n">
         <v>54.7</v>
       </c>
+      <c r="I232" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7271,6 +7929,9 @@
       <c r="H233" t="n">
         <v>54.7</v>
       </c>
+      <c r="I233" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7301,6 +7962,9 @@
       <c r="H234" t="n">
         <v>54.7</v>
       </c>
+      <c r="I234" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7331,6 +7995,9 @@
       <c r="H235" t="n">
         <v>54.7</v>
       </c>
+      <c r="I235" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7361,6 +8028,7 @@
       <c r="H236" t="n">
         <v>59.3</v>
       </c>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7389,6 +8057,7 @@
       <c r="H237" t="n">
         <v>59.3</v>
       </c>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7417,6 +8086,7 @@
       <c r="H238" t="n">
         <v>59.3</v>
       </c>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7447,6 +8117,7 @@
       <c r="H239" t="n">
         <v>59.3</v>
       </c>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7475,6 +8146,9 @@
       <c r="H240" t="n">
         <v>89.90000000000001</v>
       </c>
+      <c r="I240" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7505,6 +8179,9 @@
       <c r="H241" t="n">
         <v>89.90000000000001</v>
       </c>
+      <c r="I241" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7533,6 +8210,9 @@
       <c r="H242" t="n">
         <v>62.9</v>
       </c>
+      <c r="I242" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7561,6 +8241,9 @@
       <c r="H243" t="n">
         <v>62.9</v>
       </c>
+      <c r="I243" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7589,6 +8272,9 @@
       <c r="H244" t="n">
         <v>62.9</v>
       </c>
+      <c r="I244" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7617,6 +8303,9 @@
       <c r="H245" t="n">
         <v>56.9</v>
       </c>
+      <c r="I245" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7645,6 +8334,9 @@
       <c r="H246" t="n">
         <v>56.9</v>
       </c>
+      <c r="I246" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7675,6 +8367,9 @@
       <c r="H247" t="n">
         <v>56.9</v>
       </c>
+      <c r="I247" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7705,6 +8400,9 @@
       <c r="H248" t="n">
         <v>56.9</v>
       </c>
+      <c r="I248" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7735,6 +8433,9 @@
       <c r="H249" t="n">
         <v>56.9</v>
       </c>
+      <c r="I249" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7763,6 +8464,9 @@
       <c r="H250" t="n">
         <v>56.9</v>
       </c>
+      <c r="I250" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7793,6 +8497,9 @@
       <c r="H251" t="n">
         <v>83</v>
       </c>
+      <c r="I251" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7823,6 +8530,9 @@
       <c r="H252" t="n">
         <v>83</v>
       </c>
+      <c r="I252" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7853,6 +8563,9 @@
       <c r="H253" t="n">
         <v>83</v>
       </c>
+      <c r="I253" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7883,6 +8596,9 @@
       <c r="H254" t="n">
         <v>83</v>
       </c>
+      <c r="I254" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7913,6 +8629,9 @@
       <c r="H255" t="n">
         <v>83</v>
       </c>
+      <c r="I255" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7943,6 +8662,9 @@
       <c r="H256" t="n">
         <v>83</v>
       </c>
+      <c r="I256" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7973,6 +8695,9 @@
       <c r="H257" t="n">
         <v>83</v>
       </c>
+      <c r="I257" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8003,6 +8728,9 @@
       <c r="H258" t="n">
         <v>83</v>
       </c>
+      <c r="I258" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8033,6 +8761,9 @@
       <c r="H259" t="n">
         <v>83</v>
       </c>
+      <c r="I259" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8063,6 +8794,9 @@
       <c r="H260" t="n">
         <v>83</v>
       </c>
+      <c r="I260" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8093,6 +8827,9 @@
       <c r="H261" t="n">
         <v>83</v>
       </c>
+      <c r="I261" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8123,6 +8860,9 @@
       <c r="H262" t="n">
         <v>83</v>
       </c>
+      <c r="I262" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8153,6 +8893,9 @@
       <c r="H263" t="n">
         <v>83</v>
       </c>
+      <c r="I263" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8181,6 +8924,9 @@
       <c r="H264" t="n">
         <v>73.3</v>
       </c>
+      <c r="I264" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8211,6 +8957,9 @@
       <c r="H265" t="n">
         <v>73.3</v>
       </c>
+      <c r="I265" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8239,6 +8988,9 @@
       <c r="H266" t="n">
         <v>73.3</v>
       </c>
+      <c r="I266" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8269,6 +9021,9 @@
       <c r="H267" t="n">
         <v>73.3</v>
       </c>
+      <c r="I267" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8299,6 +9054,7 @@
       <c r="H268" t="n">
         <v>57.9</v>
       </c>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8329,6 +9085,7 @@
       <c r="H269" t="n">
         <v>49.6</v>
       </c>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8359,6 +9116,9 @@
       <c r="H270" t="n">
         <v>57.4</v>
       </c>
+      <c r="I270" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8389,6 +9149,9 @@
       <c r="H271" t="n">
         <v>57.4</v>
       </c>
+      <c r="I271" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8419,6 +9182,9 @@
       <c r="H272" t="n">
         <v>57.4</v>
       </c>
+      <c r="I272" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8447,6 +9213,9 @@
       <c r="H273" t="n">
         <v>57.4</v>
       </c>
+      <c r="I273" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8475,6 +9244,9 @@
       <c r="H274" t="n">
         <v>57.4</v>
       </c>
+      <c r="I274" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8505,6 +9277,9 @@
       <c r="H275" t="n">
         <v>57.4</v>
       </c>
+      <c r="I275" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8535,6 +9310,9 @@
       <c r="H276" t="n">
         <v>57.4</v>
       </c>
+      <c r="I276" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8565,6 +9343,9 @@
       <c r="H277" t="n">
         <v>57.4</v>
       </c>
+      <c r="I277" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8595,6 +9376,7 @@
       <c r="H278" t="n">
         <v>61.4</v>
       </c>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8623,6 +9405,7 @@
       <c r="H279" t="n">
         <v>61.4</v>
       </c>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8651,6 +9434,7 @@
       <c r="H280" t="n">
         <v>61.4</v>
       </c>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8681,6 +9465,7 @@
       <c r="H281" t="n">
         <v>61.4</v>
       </c>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8709,6 +9494,9 @@
       <c r="H282" t="n">
         <v>91</v>
       </c>
+      <c r="I282" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8738,6 +9526,9 @@
       </c>
       <c r="H283" t="n">
         <v>91</v>
+      </c>
+      <c r="I283" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/baza_balkany.xlsx
+++ b/baza_balkany.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I283"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,9 @@
       <c r="E2" t="n">
         <v>516</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>3300</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>AL</t>
@@ -524,7 +526,9 @@
       <c r="E3" t="n">
         <v>383</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>AL</t>
@@ -555,7 +559,9 @@
       <c r="E4" t="n">
         <v>427</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>AL</t>
@@ -586,7 +592,9 @@
       <c r="E5" t="n">
         <v>185</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>BG</t>
@@ -617,7 +625,9 @@
       <c r="E6" t="n">
         <v>280</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>BG</t>
@@ -747,7 +757,9 @@
       <c r="E10" t="n">
         <v>675</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>BG</t>
@@ -1207,7 +1219,9 @@
       <c r="E24" t="n">
         <v>1501</v>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>HR</t>
@@ -1271,7 +1285,9 @@
       <c r="E26" t="n">
         <v>4535</v>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>HR</t>
@@ -1302,7 +1318,9 @@
       <c r="E27" t="n">
         <v>2394</v>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>HR</t>
@@ -1351,54 +1369,56 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MK00</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2018</v>
       </c>
       <c r="C29" t="n">
-        <v>1880077</v>
+        <v>2761016</v>
       </c>
       <c r="D29" t="n">
-        <v>1416374</v>
+        <v>515731</v>
       </c>
       <c r="E29" t="n">
-        <v>494</v>
+        <v>1028</v>
       </c>
       <c r="F29" t="n">
-        <v>2152.75</v>
+        <v>2782.13</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>50.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2018</v>
       </c>
       <c r="C30" t="n">
-        <v>2761016</v>
+        <v>4241489</v>
       </c>
       <c r="D30" t="n">
-        <v>515731</v>
+        <v>798270</v>
       </c>
       <c r="E30" t="n">
-        <v>1028</v>
+        <v>2097</v>
       </c>
       <c r="F30" t="n">
-        <v>2782.13</v>
+        <v>722.46</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1415,23 +1435,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2018</v>
       </c>
       <c r="C31" t="n">
-        <v>4241489</v>
+        <v>1685510</v>
       </c>
       <c r="D31" t="n">
-        <v>798270</v>
+        <v>248423</v>
       </c>
       <c r="E31" t="n">
-        <v>2097</v>
+        <v>913</v>
       </c>
       <c r="F31" t="n">
-        <v>722.46</v>
+        <v>1698.78</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1448,23 +1468,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2018</v>
       </c>
       <c r="C32" t="n">
-        <v>1685510</v>
+        <v>5582346</v>
       </c>
       <c r="D32" t="n">
-        <v>248423</v>
+        <v>307804</v>
       </c>
       <c r="E32" t="n">
-        <v>913</v>
+        <v>1396</v>
       </c>
       <c r="F32" t="n">
-        <v>1698.78</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1481,22 +1501,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2018</v>
       </c>
       <c r="C33" t="n">
-        <v>5582346</v>
+        <v>1819959</v>
       </c>
       <c r="D33" t="n">
-        <v>307804</v>
+        <v>337295</v>
       </c>
       <c r="E33" t="n">
-        <v>1396</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>747</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1512,22 +1534,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2018</v>
       </c>
       <c r="C34" t="n">
-        <v>1819959</v>
+        <v>3633224</v>
       </c>
       <c r="D34" t="n">
-        <v>337295</v>
+        <v>2165208</v>
       </c>
       <c r="E34" t="n">
-        <v>747</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13818.91</v>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1543,23 +1567,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2018</v>
       </c>
       <c r="C35" t="n">
-        <v>3633224</v>
+        <v>1720468</v>
       </c>
       <c r="D35" t="n">
-        <v>2165208</v>
+        <v>90110</v>
       </c>
       <c r="E35" t="n">
-        <v>220</v>
+        <v>541</v>
       </c>
       <c r="F35" t="n">
-        <v>13818.91</v>
+        <v>492.51</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1576,23 +1600,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2018</v>
       </c>
       <c r="C36" t="n">
-        <v>1720468</v>
+        <v>1891355</v>
       </c>
       <c r="D36" t="n">
-        <v>90110</v>
+        <v>391326</v>
       </c>
       <c r="E36" t="n">
-        <v>541</v>
+        <v>778</v>
       </c>
       <c r="F36" t="n">
-        <v>492.51</v>
+        <v>1517.25</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1609,55 +1633,57 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>AL01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C37" t="n">
-        <v>1891355</v>
+        <v>922258</v>
       </c>
       <c r="D37" t="n">
-        <v>391326</v>
+        <v>662348</v>
       </c>
       <c r="E37" t="n">
-        <v>778</v>
+        <v>502</v>
       </c>
       <c r="F37" t="n">
-        <v>1517.25</v>
+        <v>3500</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>50.4</v>
+        <v>51.7</v>
       </c>
       <c r="I37" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AL01</t>
+          <t>AL02</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>922258</v>
+        <v>1056231</v>
       </c>
       <c r="D38" t="n">
-        <v>662348</v>
+        <v>726529</v>
       </c>
       <c r="E38" t="n">
-        <v>502</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12</v>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>AL</t>
@@ -1673,22 +1699,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AL02</t>
+          <t>AL03</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2019</v>
       </c>
       <c r="C39" t="n">
-        <v>1056231</v>
+        <v>1023800</v>
       </c>
       <c r="D39" t="n">
-        <v>726529</v>
+        <v>598375</v>
       </c>
       <c r="E39" t="n">
-        <v>399</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
+        <v>504</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>AL</t>
@@ -1704,53 +1732,57 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AL03</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>1023800</v>
+        <v>454964</v>
       </c>
       <c r="D40" t="n">
-        <v>598375</v>
+        <v>72639</v>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>185</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>51.7</v>
+        <v>49.4</v>
       </c>
       <c r="I40" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2019</v>
       </c>
       <c r="C41" t="n">
-        <v>454964</v>
+        <v>724472</v>
       </c>
       <c r="D41" t="n">
-        <v>72639</v>
+        <v>181352</v>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>295</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>BG</t>
@@ -1766,22 +1798,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2019</v>
       </c>
       <c r="C42" t="n">
-        <v>724472</v>
+        <v>7396656</v>
       </c>
       <c r="D42" t="n">
-        <v>181352</v>
+        <v>6056915</v>
       </c>
       <c r="E42" t="n">
-        <v>295</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
+        <v>735</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2068.56</v>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>BG</t>
@@ -1797,23 +1831,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2019</v>
       </c>
       <c r="C43" t="n">
-        <v>7396656</v>
+        <v>9675585</v>
       </c>
       <c r="D43" t="n">
-        <v>6056915</v>
+        <v>7787619</v>
       </c>
       <c r="E43" t="n">
-        <v>735</v>
+        <v>1140</v>
       </c>
       <c r="F43" t="n">
-        <v>2068.56</v>
+        <v>2858.02</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1830,23 +1864,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2019</v>
       </c>
       <c r="C44" t="n">
-        <v>9675585</v>
+        <v>4207154</v>
       </c>
       <c r="D44" t="n">
-        <v>7787619</v>
+        <v>2356136</v>
       </c>
       <c r="E44" t="n">
-        <v>1140</v>
+        <v>593</v>
       </c>
       <c r="F44" t="n">
-        <v>2858.02</v>
+        <v>7078.18</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1863,23 +1897,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>4207154</v>
+        <v>2463980</v>
       </c>
       <c r="D45" t="n">
-        <v>2356136</v>
+        <v>577800</v>
       </c>
       <c r="E45" t="n">
-        <v>593</v>
+        <v>716</v>
       </c>
       <c r="F45" t="n">
-        <v>7078.18</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1896,54 +1930,56 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2019</v>
       </c>
       <c r="C46" t="n">
-        <v>2463980</v>
+        <v>10260847</v>
       </c>
       <c r="D46" t="n">
-        <v>577800</v>
+        <v>7603950</v>
       </c>
       <c r="E46" t="n">
-        <v>716</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
+        <v>1435</v>
+      </c>
+      <c r="F46" t="n">
+        <v>25577.71</v>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>49.4</v>
+        <v>84.8</v>
       </c>
       <c r="I46" t="n">
-        <v>91</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>10260847</v>
+        <v>2005706</v>
       </c>
       <c r="D47" t="n">
-        <v>7603950</v>
+        <v>1538153</v>
       </c>
       <c r="E47" t="n">
-        <v>1435</v>
+        <v>1351</v>
       </c>
       <c r="F47" t="n">
-        <v>25577.71</v>
+        <v>1346.81</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1960,23 +1996,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EL41</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2019</v>
       </c>
       <c r="C48" t="n">
-        <v>2005706</v>
+        <v>30592824</v>
       </c>
       <c r="D48" t="n">
-        <v>1538153</v>
+        <v>28701778</v>
       </c>
       <c r="E48" t="n">
-        <v>1351</v>
+        <v>9395</v>
       </c>
       <c r="F48" t="n">
-        <v>1346.81</v>
+        <v>12309.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1993,23 +2029,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2019</v>
       </c>
       <c r="C49" t="n">
-        <v>30592824</v>
+        <v>27962541</v>
       </c>
       <c r="D49" t="n">
-        <v>28701778</v>
+        <v>26760215</v>
       </c>
       <c r="E49" t="n">
-        <v>9395</v>
+        <v>5016</v>
       </c>
       <c r="F49" t="n">
-        <v>12309.99</v>
+        <v>10755.92</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2026,23 +2062,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EL43</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>2019</v>
       </c>
       <c r="C50" t="n">
-        <v>27962541</v>
+        <v>2152142</v>
       </c>
       <c r="D50" t="n">
-        <v>26760215</v>
+        <v>1362429</v>
       </c>
       <c r="E50" t="n">
-        <v>5016</v>
+        <v>1544</v>
       </c>
       <c r="F50" t="n">
-        <v>10755.92</v>
+        <v>555.9299999999999</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2059,23 +2095,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EL51</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2019</v>
       </c>
       <c r="C51" t="n">
-        <v>2152142</v>
+        <v>10809343</v>
       </c>
       <c r="D51" t="n">
-        <v>1362429</v>
+        <v>8149029</v>
       </c>
       <c r="E51" t="n">
-        <v>1544</v>
+        <v>5313</v>
       </c>
       <c r="F51" t="n">
-        <v>555.9299999999999</v>
+        <v>6679.06</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2092,23 +2128,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EL52</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>2019</v>
       </c>
       <c r="C52" t="n">
-        <v>10809343</v>
+        <v>312803</v>
       </c>
       <c r="D52" t="n">
-        <v>8149029</v>
+        <v>54593</v>
       </c>
       <c r="E52" t="n">
-        <v>5313</v>
+        <v>198</v>
       </c>
       <c r="F52" t="n">
-        <v>6679.06</v>
+        <v>8.01</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2125,23 +2161,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2019</v>
       </c>
       <c r="C53" t="n">
-        <v>312803</v>
+        <v>1558985</v>
       </c>
       <c r="D53" t="n">
-        <v>54593</v>
+        <v>707084</v>
       </c>
       <c r="E53" t="n">
-        <v>198</v>
+        <v>1730</v>
       </c>
       <c r="F53" t="n">
-        <v>8.01</v>
+        <v>133.38</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2158,23 +2194,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EL54</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2019</v>
       </c>
       <c r="C54" t="n">
-        <v>1558985</v>
+        <v>2661626</v>
       </c>
       <c r="D54" t="n">
-        <v>707084</v>
+        <v>1377455</v>
       </c>
       <c r="E54" t="n">
-        <v>1730</v>
+        <v>2311</v>
       </c>
       <c r="F54" t="n">
-        <v>133.38</v>
+        <v>469.22</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2191,23 +2227,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EL61</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>2661626</v>
+        <v>12790429</v>
       </c>
       <c r="D55" t="n">
-        <v>1377455</v>
+        <v>11909411</v>
       </c>
       <c r="E55" t="n">
-        <v>2311</v>
+        <v>5226</v>
       </c>
       <c r="F55" t="n">
-        <v>469.22</v>
+        <v>5559.42</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2224,23 +2260,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EL62</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>12790429</v>
+        <v>1999273</v>
       </c>
       <c r="D56" t="n">
-        <v>11909411</v>
+        <v>1103142</v>
       </c>
       <c r="E56" t="n">
-        <v>5226</v>
+        <v>531</v>
       </c>
       <c r="F56" t="n">
-        <v>5559.42</v>
+        <v>763.55</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2257,23 +2293,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2019</v>
       </c>
       <c r="C57" t="n">
-        <v>1999273</v>
+        <v>2163593</v>
       </c>
       <c r="D57" t="n">
-        <v>1103142</v>
+        <v>1057580</v>
       </c>
       <c r="E57" t="n">
-        <v>531</v>
+        <v>1753</v>
       </c>
       <c r="F57" t="n">
-        <v>763.55</v>
+        <v>17.45</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2290,23 +2326,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2019</v>
       </c>
       <c r="C58" t="n">
-        <v>2163593</v>
+        <v>3936868</v>
       </c>
       <c r="D58" t="n">
-        <v>1057580</v>
+        <v>2080501</v>
       </c>
       <c r="E58" t="n">
-        <v>1753</v>
+        <v>2024</v>
       </c>
       <c r="F58" t="n">
-        <v>17.45</v>
+        <v>341.28</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2323,55 +2359,57 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2019</v>
       </c>
       <c r="C59" t="n">
-        <v>3936868</v>
+        <v>420640</v>
       </c>
       <c r="D59" t="n">
-        <v>2080501</v>
+        <v>227673</v>
       </c>
       <c r="E59" t="n">
-        <v>2024</v>
+        <v>1759</v>
       </c>
       <c r="F59" t="n">
-        <v>341.28</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>84.8</v>
+        <v>67</v>
       </c>
       <c r="I59" t="n">
-        <v>1631</v>
+        <v>953</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>2019</v>
       </c>
       <c r="C60" t="n">
-        <v>420640</v>
+        <v>23204950</v>
       </c>
       <c r="D60" t="n">
-        <v>227673</v>
+        <v>21175233</v>
       </c>
       <c r="E60" t="n">
-        <v>1759</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
+        <v>108614</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7691.4</v>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>HR</t>
@@ -2387,23 +2425,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>HR04</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2019</v>
       </c>
       <c r="C61" t="n">
-        <v>23204950</v>
+        <v>2699843</v>
       </c>
       <c r="D61" t="n">
-        <v>21175233</v>
+        <v>1984833</v>
       </c>
       <c r="E61" t="n">
-        <v>108614</v>
+        <v>5147</v>
       </c>
       <c r="F61" t="n">
-        <v>7691.4</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2420,22 +2458,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HR04</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>2699843</v>
+        <v>1631267</v>
       </c>
       <c r="D62" t="n">
-        <v>1984833</v>
+        <v>1398793</v>
       </c>
       <c r="E62" t="n">
-        <v>5147</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
+        <v>2607</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>HR</t>
@@ -2451,22 +2491,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HR05</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2019</v>
       </c>
       <c r="C63" t="n">
-        <v>1631267</v>
+        <v>647936</v>
       </c>
       <c r="D63" t="n">
-        <v>1398793</v>
+        <v>358367</v>
       </c>
       <c r="E63" t="n">
-        <v>2607</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
+        <v>781</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3409.94</v>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>HR</t>
@@ -2482,87 +2524,89 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HR06</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2019</v>
       </c>
       <c r="C64" t="n">
-        <v>647936</v>
+        <v>2898938</v>
       </c>
       <c r="D64" t="n">
-        <v>358367</v>
+        <v>479593</v>
       </c>
       <c r="E64" t="n">
-        <v>781</v>
+        <v>1045</v>
       </c>
       <c r="F64" t="n">
-        <v>3409.94</v>
+        <v>2977.9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>67</v>
+        <v>50.4</v>
       </c>
       <c r="I64" t="n">
-        <v>953</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MK00</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>1975258</v>
+        <v>4491296</v>
       </c>
       <c r="D65" t="n">
-        <v>1499113</v>
+        <v>760828</v>
       </c>
       <c r="E65" t="n">
-        <v>512</v>
+        <v>2244</v>
       </c>
       <c r="F65" t="n">
-        <v>2353.33</v>
+        <v>904.9400000000001</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
+        <v>50.4</v>
+      </c>
+      <c r="I65" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2019</v>
       </c>
       <c r="C66" t="n">
-        <v>2898938</v>
+        <v>1796788</v>
       </c>
       <c r="D66" t="n">
-        <v>479593</v>
+        <v>244983</v>
       </c>
       <c r="E66" t="n">
-        <v>1045</v>
+        <v>962</v>
       </c>
       <c r="F66" t="n">
-        <v>2977.9</v>
+        <v>2098.56</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2579,23 +2623,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2019</v>
       </c>
       <c r="C67" t="n">
-        <v>4491296</v>
+        <v>5687483</v>
       </c>
       <c r="D67" t="n">
-        <v>760828</v>
+        <v>314234</v>
       </c>
       <c r="E67" t="n">
-        <v>2244</v>
+        <v>1587</v>
       </c>
       <c r="F67" t="n">
-        <v>904.9400000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2612,23 +2656,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>1796788</v>
+        <v>1854213</v>
       </c>
       <c r="D68" t="n">
-        <v>244983</v>
+        <v>284096</v>
       </c>
       <c r="E68" t="n">
-        <v>962</v>
+        <v>791</v>
       </c>
       <c r="F68" t="n">
-        <v>2098.56</v>
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2645,23 +2689,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2019</v>
       </c>
       <c r="C69" t="n">
-        <v>5687483</v>
+        <v>3780290</v>
       </c>
       <c r="D69" t="n">
-        <v>314234</v>
+        <v>2249540</v>
       </c>
       <c r="E69" t="n">
-        <v>1587</v>
+        <v>210</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04</v>
+        <v>14694.18</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2678,22 +2722,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2019</v>
       </c>
       <c r="C70" t="n">
-        <v>1854213</v>
+        <v>1833283</v>
       </c>
       <c r="D70" t="n">
-        <v>284096</v>
+        <v>83225</v>
       </c>
       <c r="E70" t="n">
-        <v>791</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
+        <v>569</v>
+      </c>
+      <c r="F70" t="n">
+        <v>514.11</v>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>RO</t>
@@ -2709,23 +2755,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>3780290</v>
+        <v>1986410</v>
       </c>
       <c r="D71" t="n">
-        <v>2249540</v>
+        <v>387539</v>
       </c>
       <c r="E71" t="n">
-        <v>210</v>
+        <v>794</v>
       </c>
       <c r="F71" t="n">
-        <v>14694.18</v>
+        <v>1594.81</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2742,152 +2788,156 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2019</v>
       </c>
       <c r="C72" t="n">
-        <v>1833283</v>
+        <v>3096826</v>
       </c>
       <c r="D72" t="n">
-        <v>83225</v>
+        <v>1864025</v>
       </c>
       <c r="E72" t="n">
-        <v>569</v>
+        <v>2314</v>
       </c>
       <c r="F72" t="n">
-        <v>514.11</v>
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>50.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2019</v>
       </c>
       <c r="C73" t="n">
-        <v>1986410</v>
+        <v>5166288</v>
       </c>
       <c r="D73" t="n">
-        <v>387539</v>
+        <v>4262297</v>
       </c>
       <c r="E73" t="n">
-        <v>794</v>
+        <v>7253</v>
       </c>
       <c r="F73" t="n">
-        <v>1594.81</v>
+        <v>1719.04</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>50.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>AL01</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C74" t="n">
-        <v>3096826</v>
+        <v>379698</v>
       </c>
       <c r="D74" t="n">
-        <v>1864025</v>
+        <v>230943</v>
       </c>
       <c r="E74" t="n">
-        <v>2314</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
+        <v>398</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1300</v>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>86.40000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>AL02</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C75" t="n">
-        <v>5166288</v>
+        <v>473246</v>
       </c>
       <c r="D75" t="n">
-        <v>4262297</v>
+        <v>308692</v>
       </c>
       <c r="E75" t="n">
-        <v>7253</v>
+        <v>467</v>
       </c>
       <c r="F75" t="n">
-        <v>1719.04</v>
+        <v>5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>86.40000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AL01</t>
+          <t>AL03</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2020</v>
       </c>
       <c r="C76" t="n">
-        <v>379698</v>
+        <v>625078</v>
       </c>
       <c r="D76" t="n">
-        <v>230943</v>
+        <v>208728</v>
       </c>
       <c r="E76" t="n">
-        <v>398</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
+        <v>592</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>AL</t>
@@ -2903,84 +2953,90 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AL02</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2020</v>
       </c>
       <c r="C77" t="n">
-        <v>473246</v>
+        <v>456173</v>
       </c>
       <c r="D77" t="n">
-        <v>308692</v>
+        <v>151260</v>
       </c>
       <c r="E77" t="n">
-        <v>467</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
+        <v>177</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="I77" t="n">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AL03</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2020</v>
       </c>
       <c r="C78" t="n">
-        <v>625078</v>
+        <v>419053</v>
       </c>
       <c r="D78" t="n">
-        <v>208728</v>
+        <v>84202</v>
       </c>
       <c r="E78" t="n">
-        <v>592</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
+        <v>286</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="I78" t="n">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2020</v>
       </c>
       <c r="C79" t="n">
-        <v>456173</v>
+        <v>2584259</v>
       </c>
       <c r="D79" t="n">
-        <v>151260</v>
+        <v>1549175</v>
       </c>
       <c r="E79" t="n">
-        <v>177</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
+        <v>627</v>
+      </c>
+      <c r="F79" t="n">
+        <v>617.53</v>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>BG</t>
@@ -2996,22 +3052,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2020</v>
       </c>
       <c r="C80" t="n">
-        <v>419053</v>
+        <v>3343827</v>
       </c>
       <c r="D80" t="n">
-        <v>84202</v>
+        <v>1478413</v>
       </c>
       <c r="E80" t="n">
-        <v>286</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
+        <v>918</v>
+      </c>
+      <c r="F80" t="n">
+        <v>413.62</v>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>BG</t>
@@ -3027,23 +3085,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2020</v>
       </c>
       <c r="C81" t="n">
-        <v>2584259</v>
+        <v>2141503</v>
       </c>
       <c r="D81" t="n">
-        <v>1549175</v>
+        <v>1013067</v>
       </c>
       <c r="E81" t="n">
-        <v>627</v>
+        <v>577</v>
       </c>
       <c r="F81" t="n">
-        <v>617.53</v>
+        <v>2830.63</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3060,23 +3118,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2020</v>
       </c>
       <c r="C82" t="n">
-        <v>3343827</v>
+        <v>1578658</v>
       </c>
       <c r="D82" t="n">
-        <v>1478413</v>
+        <v>251306</v>
       </c>
       <c r="E82" t="n">
-        <v>918</v>
+        <v>732</v>
       </c>
       <c r="F82" t="n">
-        <v>413.62</v>
+        <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3093,87 +3151,89 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2020</v>
       </c>
       <c r="C83" t="n">
-        <v>2141503</v>
+        <v>2969501</v>
       </c>
       <c r="D83" t="n">
-        <v>1013067</v>
+        <v>1790303</v>
       </c>
       <c r="E83" t="n">
-        <v>577</v>
+        <v>1041</v>
       </c>
       <c r="F83" t="n">
-        <v>2830.63</v>
+        <v>8772.24</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>51.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>92</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2020</v>
       </c>
       <c r="C84" t="n">
-        <v>1578658</v>
+        <v>498509</v>
       </c>
       <c r="D84" t="n">
-        <v>251306</v>
+        <v>203476</v>
       </c>
       <c r="E84" t="n">
-        <v>732</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
+        <v>829</v>
+      </c>
+      <c r="F84" t="n">
+        <v>575.72</v>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>51.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>92</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2020</v>
       </c>
       <c r="C85" t="n">
-        <v>2969501</v>
+        <v>8229958</v>
       </c>
       <c r="D85" t="n">
-        <v>1790303</v>
+        <v>7342324</v>
       </c>
       <c r="E85" t="n">
-        <v>1041</v>
+        <v>4794</v>
       </c>
       <c r="F85" t="n">
-        <v>8772.24</v>
+        <v>3690.47</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3190,23 +3250,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EL41</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>498509</v>
+        <v>7083131</v>
       </c>
       <c r="D86" t="n">
-        <v>203476</v>
+        <v>6561087</v>
       </c>
       <c r="E86" t="n">
-        <v>829</v>
+        <v>2907</v>
       </c>
       <c r="F86" t="n">
-        <v>575.72</v>
+        <v>3091.69</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3223,23 +3283,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2020</v>
       </c>
       <c r="C87" t="n">
-        <v>8229958</v>
+        <v>791918</v>
       </c>
       <c r="D87" t="n">
-        <v>7342324</v>
+        <v>310766</v>
       </c>
       <c r="E87" t="n">
-        <v>4794</v>
+        <v>1065</v>
       </c>
       <c r="F87" t="n">
-        <v>3690.47</v>
+        <v>203.35</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3256,23 +3316,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EL43</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2020</v>
       </c>
       <c r="C88" t="n">
-        <v>7083131</v>
+        <v>2773076</v>
       </c>
       <c r="D88" t="n">
-        <v>6561087</v>
+        <v>1486463</v>
       </c>
       <c r="E88" t="n">
-        <v>2907</v>
+        <v>3415</v>
       </c>
       <c r="F88" t="n">
-        <v>3091.69</v>
+        <v>2325.75</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3289,23 +3349,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EL51</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2020</v>
       </c>
       <c r="C89" t="n">
-        <v>791918</v>
+        <v>140050</v>
       </c>
       <c r="D89" t="n">
-        <v>310766</v>
+        <v>18207</v>
       </c>
       <c r="E89" t="n">
-        <v>1065</v>
+        <v>155</v>
       </c>
       <c r="F89" t="n">
-        <v>203.35</v>
+        <v>3.24</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3322,23 +3382,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EL52</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2020</v>
       </c>
       <c r="C90" t="n">
-        <v>2773076</v>
+        <v>638628</v>
       </c>
       <c r="D90" t="n">
-        <v>1486463</v>
+        <v>155309</v>
       </c>
       <c r="E90" t="n">
-        <v>3415</v>
+        <v>1215</v>
       </c>
       <c r="F90" t="n">
-        <v>2325.75</v>
+        <v>36.72</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3355,23 +3415,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2020</v>
       </c>
       <c r="C91" t="n">
-        <v>140050</v>
+        <v>933793</v>
       </c>
       <c r="D91" t="n">
-        <v>18207</v>
+        <v>227383</v>
       </c>
       <c r="E91" t="n">
-        <v>155</v>
+        <v>1520</v>
       </c>
       <c r="F91" t="n">
-        <v>3.24</v>
+        <v>104.41</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3388,23 +3448,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EL54</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>2020</v>
       </c>
       <c r="C92" t="n">
-        <v>638628</v>
+        <v>3332132</v>
       </c>
       <c r="D92" t="n">
-        <v>155309</v>
+        <v>2954124</v>
       </c>
       <c r="E92" t="n">
-        <v>1215</v>
+        <v>3076</v>
       </c>
       <c r="F92" t="n">
-        <v>36.72</v>
+        <v>1619.72</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3421,23 +3481,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EL61</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>2020</v>
       </c>
       <c r="C93" t="n">
-        <v>933793</v>
+        <v>727800</v>
       </c>
       <c r="D93" t="n">
-        <v>227383</v>
+        <v>215286</v>
       </c>
       <c r="E93" t="n">
-        <v>1520</v>
+        <v>392</v>
       </c>
       <c r="F93" t="n">
-        <v>104.41</v>
+        <v>203.31</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3454,23 +3514,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EL62</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2020</v>
       </c>
       <c r="C94" t="n">
-        <v>3332132</v>
+        <v>799661</v>
       </c>
       <c r="D94" t="n">
-        <v>2954124</v>
+        <v>205096</v>
       </c>
       <c r="E94" t="n">
-        <v>3076</v>
+        <v>1131</v>
       </c>
       <c r="F94" t="n">
-        <v>1619.72</v>
+        <v>8.68</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3487,23 +3547,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2020</v>
       </c>
       <c r="C95" t="n">
-        <v>727800</v>
+        <v>1458007</v>
       </c>
       <c r="D95" t="n">
-        <v>215286</v>
+        <v>350747</v>
       </c>
       <c r="E95" t="n">
-        <v>392</v>
+        <v>1588</v>
       </c>
       <c r="F95" t="n">
-        <v>203.31</v>
+        <v>88.12</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3520,88 +3580,90 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2020</v>
       </c>
       <c r="C96" t="n">
-        <v>799661</v>
+        <v>156138</v>
       </c>
       <c r="D96" t="n">
-        <v>205096</v>
+        <v>61070</v>
       </c>
       <c r="E96" t="n">
-        <v>1131</v>
+        <v>1673</v>
       </c>
       <c r="F96" t="n">
-        <v>8.68</v>
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>85.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>1631</v>
+        <v>894</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>2020</v>
       </c>
       <c r="C97" t="n">
-        <v>1458007</v>
+        <v>6160529</v>
       </c>
       <c r="D97" t="n">
-        <v>350747</v>
+        <v>4888960</v>
       </c>
       <c r="E97" t="n">
-        <v>1588</v>
+        <v>94566</v>
       </c>
       <c r="F97" t="n">
-        <v>88.12</v>
+        <v>1195.04</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>85.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I97" t="n">
-        <v>1631</v>
+        <v>894</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>2020</v>
       </c>
       <c r="C98" t="n">
-        <v>156138</v>
+        <v>391026</v>
       </c>
       <c r="D98" t="n">
-        <v>61070</v>
+        <v>279093</v>
       </c>
       <c r="E98" t="n">
-        <v>1673</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
+        <v>2209</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>HR</t>
@@ -3617,23 +3679,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2020</v>
       </c>
       <c r="C99" t="n">
-        <v>6160529</v>
+        <v>292724</v>
       </c>
       <c r="D99" t="n">
-        <v>4888960</v>
+        <v>117068</v>
       </c>
       <c r="E99" t="n">
-        <v>94566</v>
+        <v>822</v>
       </c>
       <c r="F99" t="n">
-        <v>1195.04</v>
+        <v>913.7</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3650,118 +3712,122 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HR05</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>2020</v>
       </c>
       <c r="C100" t="n">
-        <v>391026</v>
+        <v>1201556</v>
       </c>
       <c r="D100" t="n">
-        <v>279093</v>
+        <v>84094</v>
       </c>
       <c r="E100" t="n">
-        <v>2209</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
+        <v>1137</v>
+      </c>
+      <c r="F100" t="n">
+        <v>939.53</v>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>66.09999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="I100" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HR06</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>2020</v>
       </c>
       <c r="C101" t="n">
-        <v>292724</v>
+        <v>2073709</v>
       </c>
       <c r="D101" t="n">
-        <v>117068</v>
+        <v>125526</v>
       </c>
       <c r="E101" t="n">
-        <v>822</v>
+        <v>2280</v>
       </c>
       <c r="F101" t="n">
-        <v>913.7</v>
+        <v>253.75</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>66.09999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="I101" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MK00</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>2020</v>
       </c>
       <c r="C102" t="n">
-        <v>704731</v>
+        <v>808687</v>
       </c>
       <c r="D102" t="n">
-        <v>234312</v>
+        <v>56308</v>
       </c>
       <c r="E102" t="n">
-        <v>516</v>
+        <v>1057</v>
       </c>
       <c r="F102" t="n">
-        <v>709.24</v>
+        <v>777.83</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="I102" t="inlineStr"/>
+        <v>49.4</v>
+      </c>
+      <c r="I102" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>2020</v>
       </c>
       <c r="C103" t="n">
-        <v>1201556</v>
+        <v>3618959</v>
       </c>
       <c r="D103" t="n">
-        <v>84094</v>
+        <v>65596</v>
       </c>
       <c r="E103" t="n">
-        <v>1137</v>
+        <v>1566</v>
       </c>
       <c r="F103" t="n">
-        <v>939.53</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3778,23 +3844,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>2020</v>
       </c>
       <c r="C104" t="n">
-        <v>2073709</v>
+        <v>868512</v>
       </c>
       <c r="D104" t="n">
-        <v>125526</v>
+        <v>61040</v>
       </c>
       <c r="E104" t="n">
-        <v>2280</v>
+        <v>748</v>
       </c>
       <c r="F104" t="n">
-        <v>253.75</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3811,23 +3877,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>2020</v>
       </c>
       <c r="C105" t="n">
-        <v>808687</v>
+        <v>1031757</v>
       </c>
       <c r="D105" t="n">
-        <v>56308</v>
+        <v>422906</v>
       </c>
       <c r="E105" t="n">
-        <v>1057</v>
+        <v>194</v>
       </c>
       <c r="F105" t="n">
-        <v>777.83</v>
+        <v>4450.63</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3844,22 +3910,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>2020</v>
       </c>
       <c r="C106" t="n">
-        <v>3618959</v>
+        <v>893524</v>
       </c>
       <c r="D106" t="n">
-        <v>65596</v>
+        <v>24291</v>
       </c>
       <c r="E106" t="n">
-        <v>1566</v>
-      </c>
-      <c r="F106" t="inlineStr"/>
+        <v>567</v>
+      </c>
+      <c r="F106" t="n">
+        <v>159.11</v>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>RO</t>
@@ -3875,22 +3943,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>2020</v>
       </c>
       <c r="C107" t="n">
-        <v>868512</v>
+        <v>824176</v>
       </c>
       <c r="D107" t="n">
-        <v>61040</v>
+        <v>91870</v>
       </c>
       <c r="E107" t="n">
-        <v>748</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
+        <v>813</v>
+      </c>
+      <c r="F107" t="n">
+        <v>470.53</v>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>RO</t>
@@ -3906,579 +3976,617 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>AL01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C108" t="n">
-        <v>1031757</v>
+        <v>745460</v>
       </c>
       <c r="D108" t="n">
-        <v>422906</v>
+        <v>539233</v>
       </c>
       <c r="E108" t="n">
-        <v>194</v>
+        <v>398</v>
       </c>
       <c r="F108" t="n">
-        <v>4450.63</v>
+        <v>2900</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>49.4</v>
+        <v>54.2</v>
       </c>
       <c r="I108" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>AL02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C109" t="n">
-        <v>893524</v>
+        <v>1121689</v>
       </c>
       <c r="D109" t="n">
-        <v>24291</v>
+        <v>876242</v>
       </c>
       <c r="E109" t="n">
-        <v>567</v>
+        <v>467</v>
       </c>
       <c r="F109" t="n">
-        <v>159.11</v>
+        <v>15</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>49.4</v>
+        <v>54.2</v>
       </c>
       <c r="I109" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>AL03</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C110" t="n">
-        <v>824176</v>
+        <v>1141556</v>
       </c>
       <c r="D110" t="n">
-        <v>91870</v>
+        <v>516622</v>
       </c>
       <c r="E110" t="n">
-        <v>813</v>
+        <v>592</v>
       </c>
       <c r="F110" t="n">
-        <v>470.53</v>
+        <v>8</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>49.4</v>
+        <v>54.2</v>
       </c>
       <c r="I110" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RS11</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C111" t="n">
-        <v>742727</v>
+        <v>448656</v>
       </c>
       <c r="D111" t="n">
-        <v>525341</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
+        <v>45161</v>
+      </c>
+      <c r="E111" t="n">
+        <v>169</v>
+      </c>
       <c r="F111" t="n">
-        <v>1784.27</v>
+        <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I111" t="inlineStr"/>
+        <v>51.6</v>
+      </c>
+      <c r="I111" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RS12</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C112" t="n">
-        <v>522428</v>
+        <v>526671</v>
       </c>
       <c r="D112" t="n">
-        <v>138147</v>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+        <v>72808</v>
+      </c>
+      <c r="E112" t="n">
+        <v>279</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
+        <v>51.6</v>
+      </c>
+      <c r="I112" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RS21</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C113" t="n">
-        <v>1706104</v>
+        <v>4278371</v>
       </c>
       <c r="D113" t="n">
-        <v>241490</v>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+        <v>3047924</v>
+      </c>
+      <c r="E113" t="n">
+        <v>644</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1055.96</v>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
+        <v>51.6</v>
+      </c>
+      <c r="I113" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RS22</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C114" t="n">
-        <v>651926</v>
+        <v>6051141</v>
       </c>
       <c r="D114" t="n">
-        <v>128107</v>
-      </c>
-      <c r="E114" t="inlineStr"/>
+        <v>3496767</v>
+      </c>
+      <c r="E114" t="n">
+        <v>972</v>
+      </c>
       <c r="F114" t="n">
-        <v>154.21</v>
+        <v>952.9299999999999</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I114" t="inlineStr"/>
+        <v>51.6</v>
+      </c>
+      <c r="I114" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C115" t="n">
-        <v>1859755</v>
+        <v>2603928</v>
       </c>
       <c r="D115" t="n">
-        <v>479767</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+        <v>929469</v>
+      </c>
+      <c r="E115" t="n">
+        <v>536</v>
+      </c>
+      <c r="F115" t="n">
+        <v>3245.07</v>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>86.3</v>
+        <v>51.6</v>
       </c>
       <c r="I115" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C116" t="n">
-        <v>2317704</v>
+        <v>1979932</v>
       </c>
       <c r="D116" t="n">
-        <v>1081897</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
+        <v>225375</v>
+      </c>
+      <c r="E116" t="n">
+        <v>735</v>
+      </c>
       <c r="F116" t="n">
-        <v>287.79</v>
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>86.3</v>
+        <v>51.6</v>
       </c>
       <c r="I116" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AL01</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>745460</v>
+        <v>4926062</v>
       </c>
       <c r="D117" t="n">
-        <v>539233</v>
+        <v>3318037</v>
       </c>
       <c r="E117" t="n">
-        <v>398</v>
-      </c>
-      <c r="F117" t="inlineStr"/>
+        <v>956</v>
+      </c>
+      <c r="F117" t="n">
+        <v>13357.44</v>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>54.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I117" t="n">
-        <v>113</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AL02</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>2021</v>
       </c>
       <c r="C118" t="n">
-        <v>1121689</v>
+        <v>942827</v>
       </c>
       <c r="D118" t="n">
-        <v>876242</v>
+        <v>615187</v>
       </c>
       <c r="E118" t="n">
-        <v>467</v>
-      </c>
-      <c r="F118" t="inlineStr"/>
+        <v>889</v>
+      </c>
+      <c r="F118" t="n">
+        <v>876.63</v>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>54.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>113</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AL03</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>2021</v>
       </c>
       <c r="C119" t="n">
-        <v>1141556</v>
+        <v>16522661</v>
       </c>
       <c r="D119" t="n">
-        <v>516622</v>
+        <v>15315940</v>
       </c>
       <c r="E119" t="n">
-        <v>592</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
+        <v>5262</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8200.190000000001</v>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>54.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>113</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>2021</v>
       </c>
       <c r="C120" t="n">
-        <v>448656</v>
+        <v>15438808</v>
       </c>
       <c r="D120" t="n">
-        <v>45161</v>
+        <v>14639324</v>
       </c>
       <c r="E120" t="n">
-        <v>169</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="F120" t="n">
+        <v>6798.45</v>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>51.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>92</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>2021</v>
       </c>
       <c r="C121" t="n">
-        <v>526671</v>
+        <v>1238431</v>
       </c>
       <c r="D121" t="n">
-        <v>72808</v>
+        <v>714878</v>
       </c>
       <c r="E121" t="n">
-        <v>279</v>
-      </c>
-      <c r="F121" t="inlineStr"/>
+        <v>1126</v>
+      </c>
+      <c r="F121" t="n">
+        <v>311.91</v>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>51.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>92</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>2021</v>
       </c>
       <c r="C122" t="n">
-        <v>4278371</v>
+        <v>5792499</v>
       </c>
       <c r="D122" t="n">
-        <v>3047924</v>
+        <v>4218004</v>
       </c>
       <c r="E122" t="n">
-        <v>644</v>
+        <v>3710</v>
       </c>
       <c r="F122" t="n">
-        <v>1055.96</v>
+        <v>3466.38</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>51.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>92</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>2021</v>
       </c>
       <c r="C123" t="n">
-        <v>6051141</v>
+        <v>167669</v>
       </c>
       <c r="D123" t="n">
-        <v>3496767</v>
+        <v>22027</v>
       </c>
       <c r="E123" t="n">
-        <v>972</v>
+        <v>112</v>
       </c>
       <c r="F123" t="n">
-        <v>952.9299999999999</v>
+        <v>5.27</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>51.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I123" t="n">
-        <v>92</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>2021</v>
       </c>
       <c r="C124" t="n">
-        <v>2603928</v>
+        <v>803131</v>
       </c>
       <c r="D124" t="n">
-        <v>929469</v>
+        <v>276790</v>
       </c>
       <c r="E124" t="n">
-        <v>536</v>
+        <v>1049</v>
       </c>
       <c r="F124" t="n">
-        <v>3245.07</v>
+        <v>62.23</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>51.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>92</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>2021</v>
       </c>
       <c r="C125" t="n">
-        <v>1979932</v>
+        <v>1428986</v>
       </c>
       <c r="D125" t="n">
-        <v>225375</v>
+        <v>561466</v>
       </c>
       <c r="E125" t="n">
-        <v>735</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
+        <v>1451</v>
+      </c>
+      <c r="F125" t="n">
+        <v>233.57</v>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>51.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>92</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>2021</v>
       </c>
       <c r="C126" t="n">
-        <v>4926062</v>
+        <v>6769045</v>
       </c>
       <c r="D126" t="n">
-        <v>3318037</v>
+        <v>6179313</v>
       </c>
       <c r="E126" t="n">
-        <v>956</v>
+        <v>3644</v>
       </c>
       <c r="F126" t="n">
-        <v>13357.44</v>
+        <v>3387.6</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4495,23 +4603,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EL41</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>2021</v>
       </c>
       <c r="C127" t="n">
-        <v>942827</v>
+        <v>1061237</v>
       </c>
       <c r="D127" t="n">
-        <v>615187</v>
+        <v>478776</v>
       </c>
       <c r="E127" t="n">
-        <v>889</v>
+        <v>325</v>
       </c>
       <c r="F127" t="n">
-        <v>876.63</v>
+        <v>464.28</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4528,23 +4636,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>2021</v>
       </c>
       <c r="C128" t="n">
-        <v>16522661</v>
+        <v>1102170</v>
       </c>
       <c r="D128" t="n">
-        <v>15315940</v>
+        <v>426602</v>
       </c>
       <c r="E128" t="n">
-        <v>5262</v>
+        <v>991</v>
       </c>
       <c r="F128" t="n">
-        <v>8200.190000000001</v>
+        <v>13.51</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4561,23 +4669,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EL43</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>2021</v>
       </c>
       <c r="C129" t="n">
-        <v>15438808</v>
+        <v>2151118</v>
       </c>
       <c r="D129" t="n">
-        <v>14639324</v>
+        <v>804225</v>
       </c>
       <c r="E129" t="n">
-        <v>3500</v>
+        <v>1498</v>
       </c>
       <c r="F129" t="n">
-        <v>6798.45</v>
+        <v>175.83</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4594,1210 +4702,1244 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EL51</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>2021</v>
       </c>
       <c r="C130" t="n">
-        <v>1238431</v>
+        <v>264587</v>
       </c>
       <c r="D130" t="n">
-        <v>714878</v>
+        <v>112890</v>
       </c>
       <c r="E130" t="n">
-        <v>1126</v>
+        <v>1731</v>
       </c>
       <c r="F130" t="n">
-        <v>311.91</v>
+        <v>0</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>83.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I130" t="n">
-        <v>1680</v>
+        <v>894</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EL52</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>2021</v>
       </c>
       <c r="C131" t="n">
-        <v>5792499</v>
+        <v>14181948</v>
       </c>
       <c r="D131" t="n">
-        <v>4218004</v>
+        <v>12006763</v>
       </c>
       <c r="E131" t="n">
-        <v>3710</v>
+        <v>98918</v>
       </c>
       <c r="F131" t="n">
-        <v>3466.38</v>
+        <v>3288.92</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>83.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I131" t="n">
-        <v>1680</v>
+        <v>894</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>2021</v>
       </c>
       <c r="C132" t="n">
-        <v>167669</v>
+        <v>780542</v>
       </c>
       <c r="D132" t="n">
-        <v>22027</v>
+        <v>590706</v>
       </c>
       <c r="E132" t="n">
-        <v>112</v>
+        <v>1752</v>
       </c>
       <c r="F132" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>83.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I132" t="n">
-        <v>1680</v>
+        <v>894</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EL54</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>2021</v>
       </c>
       <c r="C133" t="n">
-        <v>803131</v>
+        <v>478287</v>
       </c>
       <c r="D133" t="n">
-        <v>276790</v>
+        <v>194790</v>
       </c>
       <c r="E133" t="n">
-        <v>1049</v>
+        <v>914</v>
       </c>
       <c r="F133" t="n">
-        <v>62.23</v>
+        <v>1388.67</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>83.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I133" t="n">
-        <v>1680</v>
+        <v>894</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EL61</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>2021</v>
       </c>
       <c r="C134" t="n">
-        <v>1428986</v>
+        <v>2153855</v>
       </c>
       <c r="D134" t="n">
-        <v>561466</v>
+        <v>170817</v>
       </c>
       <c r="E134" t="n">
-        <v>1451</v>
+        <v>1528</v>
       </c>
       <c r="F134" t="n">
-        <v>233.57</v>
+        <v>1456.98</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>83.90000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="I134" t="n">
-        <v>1680</v>
+        <v>49</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EL62</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>2021</v>
       </c>
       <c r="C135" t="n">
-        <v>6769045</v>
+        <v>3413902</v>
       </c>
       <c r="D135" t="n">
-        <v>6179313</v>
+        <v>266595</v>
       </c>
       <c r="E135" t="n">
-        <v>3644</v>
+        <v>2728</v>
       </c>
       <c r="F135" t="n">
-        <v>3387.6</v>
+        <v>364.1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>83.90000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="I135" t="n">
-        <v>1680</v>
+        <v>49</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>2021</v>
       </c>
       <c r="C136" t="n">
-        <v>1061237</v>
+        <v>1429005</v>
       </c>
       <c r="D136" t="n">
-        <v>478776</v>
+        <v>86243</v>
       </c>
       <c r="E136" t="n">
-        <v>325</v>
+        <v>1287</v>
       </c>
       <c r="F136" t="n">
-        <v>464.28</v>
+        <v>1364.44</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>83.90000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="I136" t="n">
-        <v>1680</v>
+        <v>49</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>2021</v>
       </c>
       <c r="C137" t="n">
-        <v>1102170</v>
+        <v>5549872</v>
       </c>
       <c r="D137" t="n">
-        <v>426602</v>
+        <v>163132</v>
       </c>
       <c r="E137" t="n">
-        <v>991</v>
+        <v>2395</v>
       </c>
       <c r="F137" t="n">
-        <v>13.51</v>
+        <v>47.06</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>83.90000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="I137" t="n">
-        <v>1680</v>
+        <v>49</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>2021</v>
       </c>
       <c r="C138" t="n">
-        <v>2151118</v>
+        <v>1286629</v>
       </c>
       <c r="D138" t="n">
-        <v>804225</v>
+        <v>95908</v>
       </c>
       <c r="E138" t="n">
-        <v>1498</v>
+        <v>977</v>
       </c>
       <c r="F138" t="n">
-        <v>175.83</v>
+        <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>83.90000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="I138" t="n">
-        <v>1680</v>
+        <v>49</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>2021</v>
       </c>
       <c r="C139" t="n">
-        <v>264587</v>
+        <v>1977400</v>
       </c>
       <c r="D139" t="n">
-        <v>112890</v>
+        <v>832154</v>
       </c>
       <c r="E139" t="n">
-        <v>1731</v>
-      </c>
-      <c r="F139" t="inlineStr"/>
+        <v>277</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6887.62</v>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>65.2</v>
+        <v>49.7</v>
       </c>
       <c r="I139" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>2021</v>
       </c>
       <c r="C140" t="n">
-        <v>14181948</v>
+        <v>1305860</v>
       </c>
       <c r="D140" t="n">
-        <v>12006763</v>
+        <v>35619</v>
       </c>
       <c r="E140" t="n">
-        <v>98918</v>
+        <v>697</v>
       </c>
       <c r="F140" t="n">
-        <v>3288.92</v>
+        <v>190.61</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>65.2</v>
+        <v>49.7</v>
       </c>
       <c r="I140" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HR05</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>2021</v>
       </c>
       <c r="C141" t="n">
-        <v>780542</v>
+        <v>1197935</v>
       </c>
       <c r="D141" t="n">
-        <v>590706</v>
+        <v>134321</v>
       </c>
       <c r="E141" t="n">
-        <v>1752</v>
-      </c>
-      <c r="F141" t="inlineStr"/>
+        <v>878</v>
+      </c>
+      <c r="F141" t="n">
+        <v>628.9299999999999</v>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>65.2</v>
+        <v>49.7</v>
       </c>
       <c r="I141" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HR06</t>
+          <t>RS11</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>2021</v>
       </c>
       <c r="C142" t="n">
-        <v>478287</v>
+        <v>1427191</v>
       </c>
       <c r="D142" t="n">
-        <v>194790</v>
+        <v>1130340</v>
       </c>
       <c r="E142" t="n">
-        <v>914</v>
+        <v>158</v>
       </c>
       <c r="F142" t="n">
-        <v>1388.67</v>
+        <v>3285.51</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>65.2</v>
+        <v>54</v>
       </c>
       <c r="I142" t="n">
-        <v>894</v>
+        <v>50</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MK00</t>
+          <t>RS12</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>2021</v>
       </c>
       <c r="C143" t="n">
-        <v>1108081</v>
+        <v>826399</v>
       </c>
       <c r="D143" t="n">
-        <v>638128</v>
+        <v>291260</v>
       </c>
       <c r="E143" t="n">
-        <v>508</v>
+        <v>621</v>
       </c>
       <c r="F143" t="n">
-        <v>1266.23</v>
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="I143" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="I143" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>RS21</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>2021</v>
       </c>
       <c r="C144" t="n">
-        <v>2153855</v>
+        <v>2124016</v>
       </c>
       <c r="D144" t="n">
-        <v>170817</v>
+        <v>422288</v>
       </c>
       <c r="E144" t="n">
-        <v>1528</v>
+        <v>1804</v>
       </c>
       <c r="F144" t="n">
-        <v>1456.98</v>
+        <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>49.7</v>
+        <v>54</v>
       </c>
       <c r="I144" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>RS22</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>2021</v>
       </c>
       <c r="C145" t="n">
-        <v>3413902</v>
+        <v>851734</v>
       </c>
       <c r="D145" t="n">
-        <v>266595</v>
+        <v>188515</v>
       </c>
       <c r="E145" t="n">
-        <v>2728</v>
+        <v>3358</v>
       </c>
       <c r="F145" t="n">
-        <v>364.1</v>
+        <v>146.28</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>49.7</v>
+        <v>54</v>
       </c>
       <c r="I145" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>2021</v>
       </c>
       <c r="C146" t="n">
-        <v>1429005</v>
+        <v>2234770</v>
       </c>
       <c r="D146" t="n">
-        <v>86243</v>
+        <v>563314</v>
       </c>
       <c r="E146" t="n">
-        <v>1287</v>
+        <v>2237</v>
       </c>
       <c r="F146" t="n">
-        <v>1364.44</v>
+        <v>0</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>49.7</v>
+        <v>87.2</v>
       </c>
       <c r="I146" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>2021</v>
       </c>
       <c r="C147" t="n">
-        <v>5549872</v>
+        <v>2998043</v>
       </c>
       <c r="D147" t="n">
-        <v>163132</v>
+        <v>1538564</v>
       </c>
       <c r="E147" t="n">
-        <v>2395</v>
+        <v>6703</v>
       </c>
       <c r="F147" t="n">
-        <v>47.06</v>
+        <v>419.35</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>49.7</v>
+        <v>87.2</v>
       </c>
       <c r="I147" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>AL01</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C148" t="n">
-        <v>1286629</v>
+        <v>858742</v>
       </c>
       <c r="D148" t="n">
-        <v>95908</v>
+        <v>597730</v>
       </c>
       <c r="E148" t="n">
-        <v>977</v>
-      </c>
-      <c r="F148" t="inlineStr"/>
+        <v>424</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4700</v>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>49.7</v>
+        <v>54.6</v>
       </c>
       <c r="I148" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>AL02</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C149" t="n">
-        <v>1977400</v>
+        <v>1548179</v>
       </c>
       <c r="D149" t="n">
-        <v>832154</v>
+        <v>1175457</v>
       </c>
       <c r="E149" t="n">
-        <v>277</v>
+        <v>480</v>
       </c>
       <c r="F149" t="n">
-        <v>6887.62</v>
+        <v>25</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>49.7</v>
+        <v>54.6</v>
       </c>
       <c r="I149" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>AL03</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C150" t="n">
-        <v>1305860</v>
+        <v>1189341</v>
       </c>
       <c r="D150" t="n">
-        <v>35619</v>
+        <v>585213</v>
       </c>
       <c r="E150" t="n">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="F150" t="n">
-        <v>190.61</v>
+        <v>12</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>49.7</v>
+        <v>54.6</v>
       </c>
       <c r="I150" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C151" t="n">
-        <v>1197935</v>
+        <v>572895</v>
       </c>
       <c r="D151" t="n">
-        <v>134321</v>
+        <v>96124</v>
       </c>
       <c r="E151" t="n">
-        <v>878</v>
+        <v>242</v>
       </c>
       <c r="F151" t="n">
-        <v>628.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>49.7</v>
+        <v>54.3</v>
       </c>
       <c r="I151" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RS11</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C152" t="n">
-        <v>1427191</v>
+        <v>647401</v>
       </c>
       <c r="D152" t="n">
-        <v>1130340</v>
+        <v>122969</v>
       </c>
       <c r="E152" t="n">
-        <v>158</v>
+        <v>342</v>
       </c>
       <c r="F152" t="n">
-        <v>3285.51</v>
+        <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>54</v>
-      </c>
-      <c r="I152" t="inlineStr"/>
+        <v>54.3</v>
+      </c>
+      <c r="I152" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RS12</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C153" t="n">
-        <v>826399</v>
+        <v>5220644</v>
       </c>
       <c r="D153" t="n">
-        <v>291260</v>
+        <v>3948317</v>
       </c>
       <c r="E153" t="n">
-        <v>621</v>
-      </c>
-      <c r="F153" t="inlineStr"/>
+        <v>693</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1474.2</v>
+      </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>54</v>
-      </c>
-      <c r="I153" t="inlineStr"/>
+        <v>54.3</v>
+      </c>
+      <c r="I153" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RS21</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C154" t="n">
-        <v>2124016</v>
+        <v>8843732</v>
       </c>
       <c r="D154" t="n">
-        <v>422288</v>
+        <v>5987278</v>
       </c>
       <c r="E154" t="n">
-        <v>1804</v>
-      </c>
-      <c r="F154" t="inlineStr"/>
+        <v>1187</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1626.28</v>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>54</v>
-      </c>
-      <c r="I154" t="inlineStr"/>
+        <v>54.3</v>
+      </c>
+      <c r="I154" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RS22</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C155" t="n">
-        <v>851734</v>
+        <v>4088445</v>
       </c>
       <c r="D155" t="n">
-        <v>188515</v>
+        <v>1986851</v>
       </c>
       <c r="E155" t="n">
-        <v>3358</v>
+        <v>684</v>
       </c>
       <c r="F155" t="n">
-        <v>146.28</v>
+        <v>5945.18</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>54</v>
-      </c>
-      <c r="I155" t="inlineStr"/>
+        <v>54.3</v>
+      </c>
+      <c r="I155" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C156" t="n">
-        <v>2234770</v>
+        <v>2743841</v>
       </c>
       <c r="D156" t="n">
-        <v>563314</v>
+        <v>415230</v>
       </c>
       <c r="E156" t="n">
-        <v>2237</v>
-      </c>
-      <c r="F156" t="inlineStr"/>
+        <v>883</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>87.2</v>
+        <v>54.3</v>
       </c>
       <c r="I156" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C157" t="n">
-        <v>2998043</v>
+        <v>9657945</v>
       </c>
       <c r="D157" t="n">
-        <v>1538564</v>
+        <v>7285123</v>
       </c>
       <c r="E157" t="n">
-        <v>6703</v>
+        <v>1186</v>
       </c>
       <c r="F157" t="n">
-        <v>419.35</v>
+        <v>24366.35</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>87.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>21</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AL01</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>2022</v>
       </c>
       <c r="C158" t="n">
-        <v>858742</v>
+        <v>1777231</v>
       </c>
       <c r="D158" t="n">
-        <v>597730</v>
+        <v>1328072</v>
       </c>
       <c r="E158" t="n">
-        <v>424</v>
-      </c>
-      <c r="F158" t="inlineStr"/>
+        <v>1053</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1361.93</v>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>54.6</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>113</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AL02</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>2022</v>
       </c>
       <c r="C159" t="n">
-        <v>1548179</v>
+        <v>28478737</v>
       </c>
       <c r="D159" t="n">
-        <v>1175457</v>
+        <v>26835038</v>
       </c>
       <c r="E159" t="n">
-        <v>480</v>
-      </c>
-      <c r="F159" t="inlineStr"/>
+        <v>6527</v>
+      </c>
+      <c r="F159" t="n">
+        <v>14053.11</v>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>54.6</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I159" t="n">
-        <v>113</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AL03</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>2022</v>
       </c>
       <c r="C160" t="n">
-        <v>1189341</v>
+        <v>26827274</v>
       </c>
       <c r="D160" t="n">
-        <v>585213</v>
+        <v>25636639</v>
       </c>
       <c r="E160" t="n">
-        <v>676</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
+        <v>4296</v>
+      </c>
+      <c r="F160" t="n">
+        <v>11249.3</v>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>54.6</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>113</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>2022</v>
       </c>
       <c r="C161" t="n">
-        <v>572895</v>
+        <v>2036923</v>
       </c>
       <c r="D161" t="n">
-        <v>96124</v>
+        <v>1311845</v>
       </c>
       <c r="E161" t="n">
-        <v>242</v>
-      </c>
-      <c r="F161" t="inlineStr"/>
+        <v>1331</v>
+      </c>
+      <c r="F161" t="n">
+        <v>507.54</v>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>54.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>92</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>2022</v>
       </c>
       <c r="C162" t="n">
-        <v>647401</v>
+        <v>9835772</v>
       </c>
       <c r="D162" t="n">
-        <v>122969</v>
+        <v>7546534</v>
       </c>
       <c r="E162" t="n">
-        <v>342</v>
-      </c>
-      <c r="F162" t="inlineStr"/>
+        <v>4420</v>
+      </c>
+      <c r="F162" t="n">
+        <v>5947.14</v>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>54.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>92</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>2022</v>
       </c>
       <c r="C163" t="n">
-        <v>5220644</v>
+        <v>248818</v>
       </c>
       <c r="D163" t="n">
-        <v>3948317</v>
+        <v>35031</v>
       </c>
       <c r="E163" t="n">
-        <v>693</v>
+        <v>175</v>
       </c>
       <c r="F163" t="n">
-        <v>1474.2</v>
+        <v>6.98</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>54.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I163" t="n">
-        <v>92</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>2022</v>
       </c>
       <c r="C164" t="n">
-        <v>8843732</v>
+        <v>1462910</v>
       </c>
       <c r="D164" t="n">
-        <v>5987278</v>
+        <v>633696</v>
       </c>
       <c r="E164" t="n">
-        <v>1187</v>
+        <v>1270</v>
       </c>
       <c r="F164" t="n">
-        <v>1626.28</v>
+        <v>92.45</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>54.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I164" t="n">
-        <v>92</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>2022</v>
       </c>
       <c r="C165" t="n">
-        <v>4088445</v>
+        <v>2414483</v>
       </c>
       <c r="D165" t="n">
-        <v>1986851</v>
+        <v>1295752</v>
       </c>
       <c r="E165" t="n">
-        <v>684</v>
+        <v>1724</v>
       </c>
       <c r="F165" t="n">
-        <v>5945.18</v>
+        <v>576.49</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>54.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I165" t="n">
-        <v>92</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>2022</v>
       </c>
       <c r="C166" t="n">
-        <v>2743841</v>
+        <v>12058229</v>
       </c>
       <c r="D166" t="n">
-        <v>415230</v>
+        <v>11286712</v>
       </c>
       <c r="E166" t="n">
-        <v>883</v>
-      </c>
-      <c r="F166" t="inlineStr"/>
+        <v>4853</v>
+      </c>
+      <c r="F166" t="n">
+        <v>6490.6</v>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>54.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>92</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>2022</v>
       </c>
       <c r="C167" t="n">
-        <v>9657945</v>
+        <v>1741135</v>
       </c>
       <c r="D167" t="n">
-        <v>7285123</v>
+        <v>861283</v>
       </c>
       <c r="E167" t="n">
-        <v>1186</v>
+        <v>461</v>
       </c>
       <c r="F167" t="n">
-        <v>24366.35</v>
+        <v>893.71</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -5814,23 +5956,23 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EL41</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>2022</v>
       </c>
       <c r="C168" t="n">
-        <v>1777231</v>
+        <v>1919741</v>
       </c>
       <c r="D168" t="n">
-        <v>1328072</v>
+        <v>862126</v>
       </c>
       <c r="E168" t="n">
-        <v>1053</v>
+        <v>1212</v>
       </c>
       <c r="F168" t="n">
-        <v>1361.93</v>
+        <v>18.75</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -5847,23 +5989,23 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>2022</v>
       </c>
       <c r="C169" t="n">
-        <v>28478737</v>
+        <v>3441825</v>
       </c>
       <c r="D169" t="n">
-        <v>26835038</v>
+        <v>1729660</v>
       </c>
       <c r="E169" t="n">
-        <v>6527</v>
+        <v>1713</v>
       </c>
       <c r="F169" t="n">
-        <v>14053.11</v>
+        <v>349.12</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -5880,3654 +6022,3135 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EL43</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>2022</v>
       </c>
       <c r="C170" t="n">
-        <v>26827274</v>
+        <v>364758</v>
       </c>
       <c r="D170" t="n">
-        <v>25636639</v>
+        <v>173596</v>
       </c>
       <c r="E170" t="n">
-        <v>4296</v>
+        <v>2020</v>
       </c>
       <c r="F170" t="n">
-        <v>11249.3</v>
+        <v>0</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>84.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="I170" t="n">
-        <v>1679</v>
+        <v>894</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EL51</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>2022</v>
       </c>
       <c r="C171" t="n">
-        <v>2036923</v>
+        <v>20709266</v>
       </c>
       <c r="D171" t="n">
-        <v>1311845</v>
+        <v>18160577</v>
       </c>
       <c r="E171" t="n">
-        <v>1331</v>
+        <v>105271</v>
       </c>
       <c r="F171" t="n">
-        <v>507.54</v>
+        <v>6651.55</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>84.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="I171" t="n">
-        <v>1679</v>
+        <v>894</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EL52</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>2022</v>
       </c>
       <c r="C172" t="n">
-        <v>9835772</v>
+        <v>1339689</v>
       </c>
       <c r="D172" t="n">
-        <v>7546534</v>
+        <v>1077049</v>
       </c>
       <c r="E172" t="n">
-        <v>4420</v>
+        <v>2105</v>
       </c>
       <c r="F172" t="n">
-        <v>5947.14</v>
+        <v>0</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>84.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="I172" t="n">
-        <v>1679</v>
+        <v>894</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>2022</v>
       </c>
       <c r="C173" t="n">
-        <v>248818</v>
+        <v>614640</v>
       </c>
       <c r="D173" t="n">
-        <v>35031</v>
+        <v>311327</v>
       </c>
       <c r="E173" t="n">
-        <v>175</v>
+        <v>1097</v>
       </c>
       <c r="F173" t="n">
-        <v>6.98</v>
+        <v>3102.49</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>84.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="I173" t="n">
-        <v>1679</v>
+        <v>894</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EL54</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>2022</v>
       </c>
       <c r="C174" t="n">
-        <v>1462910</v>
+        <v>2745262</v>
       </c>
       <c r="D174" t="n">
-        <v>633696</v>
+        <v>321661</v>
       </c>
       <c r="E174" t="n">
-        <v>1270</v>
+        <v>1650</v>
       </c>
       <c r="F174" t="n">
-        <v>92.45</v>
+        <v>2644.61</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>84.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I174" t="n">
-        <v>1679</v>
+        <v>49</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EL61</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>2022</v>
       </c>
       <c r="C175" t="n">
-        <v>2414483</v>
+        <v>4236065</v>
       </c>
       <c r="D175" t="n">
-        <v>1295752</v>
+        <v>470874</v>
       </c>
       <c r="E175" t="n">
-        <v>1724</v>
+        <v>2780</v>
       </c>
       <c r="F175" t="n">
-        <v>576.49</v>
+        <v>619.75</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>84.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I175" t="n">
-        <v>1679</v>
+        <v>49</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EL62</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>2022</v>
       </c>
       <c r="C176" t="n">
-        <v>12058229</v>
+        <v>1901648</v>
       </c>
       <c r="D176" t="n">
-        <v>11286712</v>
+        <v>213546</v>
       </c>
       <c r="E176" t="n">
-        <v>4853</v>
+        <v>1341</v>
       </c>
       <c r="F176" t="n">
-        <v>6490.6</v>
+        <v>2855.63</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>84.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I176" t="n">
-        <v>1679</v>
+        <v>49</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>2022</v>
       </c>
       <c r="C177" t="n">
-        <v>1741135</v>
+        <v>5227663</v>
       </c>
       <c r="D177" t="n">
-        <v>861283</v>
+        <v>217906</v>
       </c>
       <c r="E177" t="n">
-        <v>461</v>
+        <v>2423</v>
       </c>
       <c r="F177" t="n">
-        <v>893.71</v>
+        <v>0</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>84.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I177" t="n">
-        <v>1679</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>2022</v>
       </c>
       <c r="C178" t="n">
-        <v>1919741</v>
+        <v>1600540</v>
       </c>
       <c r="D178" t="n">
-        <v>862126</v>
+        <v>145276</v>
       </c>
       <c r="E178" t="n">
-        <v>1212</v>
+        <v>945</v>
       </c>
       <c r="F178" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>84.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I178" t="n">
-        <v>1679</v>
+        <v>49</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>2022</v>
       </c>
       <c r="C179" t="n">
-        <v>3441825</v>
+        <v>3472808</v>
       </c>
       <c r="D179" t="n">
-        <v>1729660</v>
+        <v>1783870</v>
       </c>
       <c r="E179" t="n">
-        <v>1713</v>
+        <v>288</v>
       </c>
       <c r="F179" t="n">
-        <v>349.12</v>
+        <v>12589.27</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>84.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I179" t="n">
-        <v>1679</v>
+        <v>49</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>2022</v>
       </c>
       <c r="C180" t="n">
-        <v>364758</v>
+        <v>1548345</v>
       </c>
       <c r="D180" t="n">
-        <v>173596</v>
+        <v>63118</v>
       </c>
       <c r="E180" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F180" t="inlineStr"/>
+        <v>719</v>
+      </c>
+      <c r="F180" t="n">
+        <v>475.59</v>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>68.5</v>
+        <v>53.2</v>
       </c>
       <c r="I180" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>2022</v>
       </c>
       <c r="C181" t="n">
-        <v>20709266</v>
+        <v>1452855</v>
       </c>
       <c r="D181" t="n">
-        <v>18160577</v>
+        <v>208058</v>
       </c>
       <c r="E181" t="n">
-        <v>105271</v>
+        <v>907</v>
       </c>
       <c r="F181" t="n">
-        <v>6651.55</v>
+        <v>1192.99</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>68.5</v>
+        <v>53.2</v>
       </c>
       <c r="I181" t="n">
-        <v>894</v>
+        <v>49</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HR05</t>
+          <t>RS11</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>2022</v>
       </c>
       <c r="C182" t="n">
-        <v>1339689</v>
+        <v>2069414</v>
       </c>
       <c r="D182" t="n">
-        <v>1077049</v>
+        <v>1784019</v>
       </c>
       <c r="E182" t="n">
-        <v>2105</v>
-      </c>
-      <c r="F182" t="inlineStr"/>
+        <v>2274</v>
+      </c>
+      <c r="F182" t="n">
+        <v>5610.53</v>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>68.5</v>
+        <v>57</v>
       </c>
       <c r="I182" t="n">
-        <v>894</v>
+        <v>52</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HR06</t>
+          <t>RS12</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>2022</v>
       </c>
       <c r="C183" t="n">
-        <v>614640</v>
+        <v>763078</v>
       </c>
       <c r="D183" t="n">
-        <v>311327</v>
+        <v>388905</v>
       </c>
       <c r="E183" t="n">
-        <v>1097</v>
+        <v>3406</v>
       </c>
       <c r="F183" t="n">
-        <v>3102.49</v>
+        <v>0</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>68.5</v>
+        <v>57</v>
       </c>
       <c r="I183" t="n">
-        <v>894</v>
+        <v>52</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ME00</t>
+          <t>RS21</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>2022</v>
       </c>
       <c r="C184" t="n">
-        <v>3944409</v>
+        <v>1895888</v>
       </c>
       <c r="D184" t="n">
-        <v>3599809</v>
+        <v>438120</v>
       </c>
       <c r="E184" t="n">
-        <v>419</v>
+        <v>9057</v>
       </c>
       <c r="F184" t="n">
-        <v>1908.55</v>
+        <v>0</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I184" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="I184" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MK00</t>
+          <t>RS22</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>2022</v>
       </c>
       <c r="C185" t="n">
-        <v>1597841</v>
+        <v>849663</v>
       </c>
       <c r="D185" t="n">
-        <v>1108581</v>
+        <v>236300</v>
       </c>
       <c r="E185" t="n">
-        <v>510</v>
+        <v>5727</v>
       </c>
       <c r="F185" t="n">
-        <v>2134.99</v>
+        <v>389.21</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="I185" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="I185" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>2022</v>
       </c>
       <c r="C186" t="n">
-        <v>2745262</v>
+        <v>2807732</v>
       </c>
       <c r="D186" t="n">
-        <v>321661</v>
+        <v>1311383</v>
       </c>
       <c r="E186" t="n">
-        <v>1650</v>
+        <v>2462</v>
       </c>
       <c r="F186" t="n">
-        <v>2644.61</v>
+        <v>0</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>53.2</v>
+        <v>87.8</v>
       </c>
       <c r="I186" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>2022</v>
       </c>
       <c r="C187" t="n">
-        <v>4236065</v>
+        <v>4714646</v>
       </c>
       <c r="D187" t="n">
-        <v>470874</v>
+        <v>3470397</v>
       </c>
       <c r="E187" t="n">
-        <v>2780</v>
+        <v>7490</v>
       </c>
       <c r="F187" t="n">
-        <v>619.75</v>
+        <v>968.8099999999999</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>53.2</v>
+        <v>87.8</v>
       </c>
       <c r="I187" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>AL01</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C188" t="n">
-        <v>1901648</v>
+        <v>1382523</v>
       </c>
       <c r="D188" t="n">
-        <v>213546</v>
+        <v>915167</v>
       </c>
       <c r="E188" t="n">
-        <v>1341</v>
+        <v>475</v>
       </c>
       <c r="F188" t="n">
-        <v>2855.63</v>
+        <v>5200</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>53.2</v>
+        <v>58.2</v>
       </c>
       <c r="I188" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>AL03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C189" t="n">
-        <v>5227663</v>
+        <v>2010971</v>
       </c>
       <c r="D189" t="n">
-        <v>217906</v>
+        <v>1049345</v>
       </c>
       <c r="E189" t="n">
-        <v>2423</v>
-      </c>
-      <c r="F189" t="inlineStr"/>
+        <v>782</v>
+      </c>
+      <c r="F189" t="n">
+        <v>15</v>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>53.2</v>
+        <v>58.2</v>
       </c>
       <c r="I189" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C190" t="n">
-        <v>1600540</v>
+        <v>5910027</v>
       </c>
       <c r="D190" t="n">
-        <v>145276</v>
+        <v>4622794</v>
       </c>
       <c r="E190" t="n">
-        <v>945</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1822.14</v>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>53.2</v>
+        <v>55.8</v>
       </c>
       <c r="I190" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C191" t="n">
-        <v>3472808</v>
+        <v>9534635</v>
       </c>
       <c r="D191" t="n">
-        <v>1783870</v>
+        <v>6477934</v>
       </c>
       <c r="E191" t="n">
-        <v>288</v>
+        <v>1187</v>
       </c>
       <c r="F191" t="n">
-        <v>12589.27</v>
+        <v>1826.97</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>53.2</v>
+        <v>55.8</v>
       </c>
       <c r="I191" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C192" t="n">
-        <v>1548345</v>
+        <v>4643519</v>
       </c>
       <c r="D192" t="n">
-        <v>63118</v>
+        <v>2273223</v>
       </c>
       <c r="E192" t="n">
-        <v>719</v>
+        <v>666</v>
       </c>
       <c r="F192" t="n">
-        <v>475.59</v>
+        <v>7162.36</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>53.2</v>
+        <v>55.8</v>
       </c>
       <c r="I192" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C193" t="n">
-        <v>1452855</v>
+        <v>3159863</v>
       </c>
       <c r="D193" t="n">
-        <v>208058</v>
+        <v>559986</v>
       </c>
       <c r="E193" t="n">
-        <v>907</v>
+        <v>867</v>
       </c>
       <c r="F193" t="n">
-        <v>1192.99</v>
+        <v>0</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>53.2</v>
+        <v>55.8</v>
       </c>
       <c r="I193" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RS11</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C194" t="n">
-        <v>2069414</v>
+        <v>11327339</v>
       </c>
       <c r="D194" t="n">
-        <v>1784019</v>
+        <v>8572789</v>
       </c>
       <c r="E194" t="n">
-        <v>2274</v>
+        <v>1186</v>
       </c>
       <c r="F194" t="n">
-        <v>5610.53</v>
+        <v>28175.02</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>57</v>
-      </c>
-      <c r="I194" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RS12</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C195" t="n">
-        <v>763078</v>
+        <v>2017839</v>
       </c>
       <c r="D195" t="n">
-        <v>388905</v>
+        <v>1508312</v>
       </c>
       <c r="E195" t="n">
-        <v>3406</v>
-      </c>
-      <c r="F195" t="inlineStr"/>
+        <v>1012</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1429.24</v>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>57</v>
-      </c>
-      <c r="I195" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RS21</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C196" t="n">
-        <v>1895888</v>
+        <v>29954292</v>
       </c>
       <c r="D196" t="n">
-        <v>438120</v>
+        <v>28126513</v>
       </c>
       <c r="E196" t="n">
-        <v>9057</v>
-      </c>
-      <c r="F196" t="inlineStr"/>
+        <v>6275</v>
+      </c>
+      <c r="F196" t="n">
+        <v>14359.36</v>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>57</v>
-      </c>
-      <c r="I196" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RS22</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C197" t="n">
-        <v>849663</v>
+        <v>29029567</v>
       </c>
       <c r="D197" t="n">
-        <v>236300</v>
+        <v>27688474</v>
       </c>
       <c r="E197" t="n">
-        <v>5727</v>
+        <v>4133</v>
       </c>
       <c r="F197" t="n">
-        <v>389.21</v>
+        <v>12373.26</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>57</v>
-      </c>
-      <c r="I197" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C198" t="n">
-        <v>2807732</v>
+        <v>2315351</v>
       </c>
       <c r="D198" t="n">
-        <v>1311383</v>
+        <v>1535271</v>
       </c>
       <c r="E198" t="n">
-        <v>2462</v>
-      </c>
-      <c r="F198" t="inlineStr"/>
+        <v>1277</v>
+      </c>
+      <c r="F198" t="n">
+        <v>582.0599999999999</v>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>87.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>21</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C199" t="n">
-        <v>4714646</v>
+        <v>11043573</v>
       </c>
       <c r="D199" t="n">
-        <v>3470397</v>
+        <v>8394574</v>
       </c>
       <c r="E199" t="n">
-        <v>7490</v>
+        <v>4236</v>
       </c>
       <c r="F199" t="n">
-        <v>968.8099999999999</v>
+        <v>7014.96</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>87.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I199" t="n">
-        <v>21</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AL01</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>2023</v>
       </c>
       <c r="C200" t="n">
-        <v>1382523</v>
+        <v>297067</v>
       </c>
       <c r="D200" t="n">
-        <v>915167</v>
+        <v>44736</v>
       </c>
       <c r="E200" t="n">
-        <v>475</v>
-      </c>
-      <c r="F200" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6.63</v>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>58.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>113</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AL02</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>2023</v>
       </c>
       <c r="C201" t="n">
-        <v>2189402</v>
+        <v>1741599</v>
       </c>
       <c r="D201" t="n">
-        <v>1675345</v>
-      </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
+        <v>771233</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1148</v>
+      </c>
+      <c r="F201" t="n">
+        <v>119.81</v>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>58.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>113</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AL03</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>2023</v>
       </c>
       <c r="C202" t="n">
-        <v>2010971</v>
+        <v>2656381</v>
       </c>
       <c r="D202" t="n">
-        <v>1049345</v>
+        <v>1424864</v>
       </c>
       <c r="E202" t="n">
-        <v>782</v>
-      </c>
-      <c r="F202" t="inlineStr"/>
+        <v>1611</v>
+      </c>
+      <c r="F202" t="n">
+        <v>586.47</v>
+      </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>58.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>113</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>2023</v>
       </c>
       <c r="C203" t="n">
-        <v>620373</v>
+        <v>13809340</v>
       </c>
       <c r="D203" t="n">
-        <v>125079</v>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+        <v>12932665</v>
+      </c>
+      <c r="E203" t="n">
+        <v>4527</v>
+      </c>
+      <c r="F203" t="n">
+        <v>6991.04</v>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>55.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="B204" t="n">
         <v>2023</v>
       </c>
       <c r="C204" t="n">
-        <v>663489</v>
+        <v>2117641</v>
       </c>
       <c r="D204" t="n">
-        <v>141214</v>
-      </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+        <v>1117985</v>
+      </c>
+      <c r="E204" t="n">
+        <v>439</v>
+      </c>
+      <c r="F204" t="n">
+        <v>946.08</v>
+      </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>55.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>2023</v>
       </c>
       <c r="C205" t="n">
-        <v>5910027</v>
+        <v>2228056</v>
       </c>
       <c r="D205" t="n">
-        <v>4622794</v>
+        <v>1036187</v>
       </c>
       <c r="E205" t="n">
-        <v>699</v>
+        <v>1194</v>
       </c>
       <c r="F205" t="n">
-        <v>1822.14</v>
+        <v>23.59</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>55.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="B206" t="n">
         <v>2023</v>
       </c>
       <c r="C206" t="n">
-        <v>9534635</v>
+        <v>3959584</v>
       </c>
       <c r="D206" t="n">
-        <v>6477934</v>
+        <v>1992593</v>
       </c>
       <c r="E206" t="n">
-        <v>1187</v>
+        <v>1657</v>
       </c>
       <c r="F206" t="n">
-        <v>1826.97</v>
+        <v>296.95</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>55.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>2023</v>
       </c>
       <c r="C207" t="n">
-        <v>4643519</v>
+        <v>427820</v>
       </c>
       <c r="D207" t="n">
-        <v>2273223</v>
+        <v>222666</v>
       </c>
       <c r="E207" t="n">
-        <v>666</v>
+        <v>2376</v>
       </c>
       <c r="F207" t="n">
-        <v>7162.36</v>
+        <v>0</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>55.8</v>
+        <v>71.2</v>
       </c>
       <c r="I207" t="n">
-        <v>92</v>
+        <v>894</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>2023</v>
       </c>
       <c r="C208" t="n">
-        <v>3159863</v>
+        <v>22021722</v>
       </c>
       <c r="D208" t="n">
-        <v>559986</v>
+        <v>19336013</v>
       </c>
       <c r="E208" t="n">
-        <v>867</v>
-      </c>
-      <c r="F208" t="inlineStr"/>
+        <v>111320</v>
+      </c>
+      <c r="F208" t="n">
+        <v>7518.71</v>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H208" t="n">
-        <v>55.8</v>
+        <v>71.2</v>
       </c>
       <c r="I208" t="n">
-        <v>92</v>
+        <v>894</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>2023</v>
       </c>
       <c r="C209" t="n">
-        <v>11327339</v>
+        <v>1606083</v>
       </c>
       <c r="D209" t="n">
-        <v>8572789</v>
+        <v>1309132</v>
       </c>
       <c r="E209" t="n">
-        <v>1186</v>
+        <v>2462</v>
       </c>
       <c r="F209" t="n">
-        <v>28175.02</v>
+        <v>0</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>82.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="I209" t="n">
-        <v>1728</v>
+        <v>894</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EL41</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>2023</v>
       </c>
       <c r="C210" t="n">
-        <v>2017839</v>
+        <v>661246</v>
       </c>
       <c r="D210" t="n">
-        <v>1508312</v>
+        <v>351301</v>
       </c>
       <c r="E210" t="n">
-        <v>1012</v>
+        <v>1318</v>
       </c>
       <c r="F210" t="n">
-        <v>1429.24</v>
+        <v>3696.37</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>82.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="I210" t="n">
-        <v>1728</v>
+        <v>894</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>2023</v>
       </c>
       <c r="C211" t="n">
-        <v>29954292</v>
+        <v>2924758</v>
       </c>
       <c r="D211" t="n">
-        <v>28126513</v>
+        <v>406497</v>
       </c>
       <c r="E211" t="n">
-        <v>6275</v>
+        <v>1743</v>
       </c>
       <c r="F211" t="n">
-        <v>14359.36</v>
+        <v>3238.04</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H211" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I211" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>EL43</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>2023</v>
       </c>
       <c r="C212" t="n">
-        <v>29029567</v>
+        <v>4625823</v>
       </c>
       <c r="D212" t="n">
-        <v>27688474</v>
+        <v>638479</v>
       </c>
       <c r="E212" t="n">
-        <v>4133</v>
+        <v>2948</v>
       </c>
       <c r="F212" t="n">
-        <v>12373.26</v>
+        <v>549.4400000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H212" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I212" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>EL51</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>2023</v>
       </c>
       <c r="C213" t="n">
-        <v>2315351</v>
+        <v>1948474</v>
       </c>
       <c r="D213" t="n">
-        <v>1535271</v>
+        <v>217053</v>
       </c>
       <c r="E213" t="n">
-        <v>1277</v>
+        <v>1401</v>
       </c>
       <c r="F213" t="n">
-        <v>582.0599999999999</v>
+        <v>3384.22</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H213" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I213" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EL52</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>2023</v>
       </c>
       <c r="C214" t="n">
-        <v>11043573</v>
+        <v>5726433</v>
       </c>
       <c r="D214" t="n">
-        <v>8394574</v>
+        <v>206551</v>
       </c>
       <c r="E214" t="n">
-        <v>4236</v>
+        <v>2496</v>
       </c>
       <c r="F214" t="n">
-        <v>7014.96</v>
+        <v>0</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H214" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I214" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>2023</v>
       </c>
       <c r="C215" t="n">
-        <v>297067</v>
+        <v>1842403</v>
       </c>
       <c r="D215" t="n">
-        <v>44736</v>
+        <v>209436</v>
       </c>
       <c r="E215" t="n">
-        <v>159</v>
+        <v>944</v>
       </c>
       <c r="F215" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H215" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I215" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EL54</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B216" t="n">
         <v>2023</v>
       </c>
       <c r="C216" t="n">
-        <v>1741599</v>
+        <v>3871691</v>
       </c>
       <c r="D216" t="n">
-        <v>771233</v>
+        <v>2158726</v>
       </c>
       <c r="E216" t="n">
-        <v>1148</v>
+        <v>295</v>
       </c>
       <c r="F216" t="n">
-        <v>119.81</v>
+        <v>14620.19</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H216" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I216" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EL61</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>2023</v>
       </c>
       <c r="C217" t="n">
-        <v>2656381</v>
+        <v>1781185</v>
       </c>
       <c r="D217" t="n">
-        <v>1424864</v>
+        <v>89341</v>
       </c>
       <c r="E217" t="n">
-        <v>1611</v>
+        <v>794</v>
       </c>
       <c r="F217" t="n">
-        <v>586.47</v>
+        <v>596.87</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H217" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EL62</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>2023</v>
       </c>
       <c r="C218" t="n">
-        <v>13809340</v>
+        <v>1640668</v>
       </c>
       <c r="D218" t="n">
-        <v>12932665</v>
+        <v>247845</v>
       </c>
       <c r="E218" t="n">
-        <v>4527</v>
+        <v>926</v>
       </c>
       <c r="F218" t="n">
-        <v>6991.04</v>
+        <v>1354.61</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H218" t="n">
-        <v>82.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I218" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>RS11</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>2023</v>
       </c>
       <c r="C219" t="n">
-        <v>2117641</v>
+        <v>2137233</v>
       </c>
       <c r="D219" t="n">
-        <v>1117985</v>
+        <v>1897158</v>
       </c>
       <c r="E219" t="n">
-        <v>439</v>
+        <v>2822</v>
       </c>
       <c r="F219" t="n">
-        <v>946.08</v>
+        <v>7949.35</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H219" t="n">
-        <v>82.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="I219" t="n">
-        <v>1728</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>RS12</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>2023</v>
       </c>
       <c r="C220" t="n">
-        <v>2228056</v>
+        <v>758862</v>
       </c>
       <c r="D220" t="n">
-        <v>1036187</v>
+        <v>420722</v>
       </c>
       <c r="E220" t="n">
-        <v>1194</v>
+        <v>4167</v>
       </c>
       <c r="F220" t="n">
-        <v>23.59</v>
+        <v>0</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H220" t="n">
-        <v>82.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="I220" t="n">
-        <v>1728</v>
+        <v>55</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>RS21</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>2023</v>
       </c>
       <c r="C221" t="n">
-        <v>3959584</v>
+        <v>1809907</v>
       </c>
       <c r="D221" t="n">
-        <v>1992593</v>
+        <v>501702</v>
       </c>
       <c r="E221" t="n">
-        <v>1657</v>
+        <v>10631</v>
       </c>
       <c r="F221" t="n">
-        <v>296.95</v>
+        <v>0</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H221" t="n">
-        <v>82.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="I221" t="n">
-        <v>1728</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>RS22</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>2023</v>
       </c>
       <c r="C222" t="n">
-        <v>427820</v>
+        <v>917342</v>
       </c>
       <c r="D222" t="n">
-        <v>222666</v>
+        <v>317203</v>
       </c>
       <c r="E222" t="n">
-        <v>2376</v>
-      </c>
-      <c r="F222" t="inlineStr"/>
+        <v>6622</v>
+      </c>
+      <c r="F222" t="n">
+        <v>448.02</v>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H222" t="n">
-        <v>71.2</v>
+        <v>59.3</v>
       </c>
       <c r="I222" t="n">
-        <v>894</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HR03</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>2023</v>
       </c>
       <c r="C223" t="n">
-        <v>22021722</v>
+        <v>2828659</v>
       </c>
       <c r="D223" t="n">
-        <v>19336013</v>
+        <v>1540535</v>
       </c>
       <c r="E223" t="n">
-        <v>111320</v>
+        <v>2679</v>
       </c>
       <c r="F223" t="n">
-        <v>7518.71</v>
+        <v>0</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H223" t="n">
-        <v>71.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I223" t="n">
-        <v>894</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HR05</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>2023</v>
       </c>
       <c r="C224" t="n">
-        <v>1606083</v>
+        <v>5071764</v>
       </c>
       <c r="D224" t="n">
-        <v>1309132</v>
+        <v>4050390</v>
       </c>
       <c r="E224" t="n">
-        <v>2462</v>
-      </c>
-      <c r="F224" t="inlineStr"/>
+        <v>8181</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1268.35</v>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H224" t="n">
-        <v>71.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>894</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HR06</t>
+          <t>AL01</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C225" t="n">
-        <v>661246</v>
+        <v>1529990</v>
       </c>
       <c r="D225" t="n">
-        <v>351301</v>
+        <v>1028712</v>
       </c>
       <c r="E225" t="n">
-        <v>1318</v>
+        <v>540</v>
       </c>
       <c r="F225" t="n">
-        <v>3696.37</v>
+        <v>5500</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H225" t="n">
-        <v>71.2</v>
+        <v>62.9</v>
       </c>
       <c r="I225" t="n">
-        <v>894</v>
+        <v>113</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ME00</t>
+          <t>AL02</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C226" t="n">
-        <v>4763931</v>
+        <v>2995317</v>
       </c>
       <c r="D226" t="n">
-        <v>4351671</v>
+        <v>2396565</v>
       </c>
       <c r="E226" t="n">
-        <v>453</v>
+        <v>589</v>
       </c>
       <c r="F226" t="n">
-        <v>2493.21</v>
+        <v>35</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H226" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="I226" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="I226" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MK00</t>
+          <t>AL03</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C227" t="n">
-        <v>1840127</v>
+        <v>2385161</v>
       </c>
       <c r="D227" t="n">
-        <v>1358470</v>
+        <v>1445516</v>
       </c>
       <c r="E227" t="n">
-        <v>518</v>
+        <v>969</v>
       </c>
       <c r="F227" t="n">
-        <v>3142.51</v>
+        <v>18</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="I227" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="I227" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C228" t="n">
-        <v>2924758</v>
+        <v>607563</v>
       </c>
       <c r="D228" t="n">
-        <v>406497</v>
+        <v>81127</v>
       </c>
       <c r="E228" t="n">
-        <v>1743</v>
+        <v>268</v>
       </c>
       <c r="F228" t="n">
-        <v>3238.04</v>
+        <v>0</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>54.7</v>
+        <v>56.9</v>
       </c>
       <c r="I228" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C229" t="n">
-        <v>4625823</v>
+        <v>643417</v>
       </c>
       <c r="D229" t="n">
-        <v>638479</v>
+        <v>130122</v>
       </c>
       <c r="E229" t="n">
-        <v>2948</v>
+        <v>385</v>
       </c>
       <c r="F229" t="n">
-        <v>549.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>54.7</v>
+        <v>56.9</v>
       </c>
       <c r="I229" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>BG33</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C230" t="n">
-        <v>1948474</v>
+        <v>6250742</v>
       </c>
       <c r="D230" t="n">
-        <v>217053</v>
+        <v>4869399</v>
       </c>
       <c r="E230" t="n">
-        <v>1401</v>
+        <v>703</v>
       </c>
       <c r="F230" t="n">
-        <v>3384.22</v>
+        <v>1534.75</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>54.7</v>
+        <v>56.9</v>
       </c>
       <c r="I230" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C231" t="n">
-        <v>5726433</v>
+        <v>9875732</v>
       </c>
       <c r="D231" t="n">
-        <v>206551</v>
+        <v>6802140</v>
       </c>
       <c r="E231" t="n">
-        <v>2496</v>
-      </c>
-      <c r="F231" t="inlineStr"/>
+        <v>1148</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1781.24</v>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H231" t="n">
-        <v>54.7</v>
+        <v>56.9</v>
       </c>
       <c r="I231" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>BG41</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C232" t="n">
-        <v>1842403</v>
+        <v>4754940</v>
       </c>
       <c r="D232" t="n">
-        <v>209436</v>
+        <v>2348979</v>
       </c>
       <c r="E232" t="n">
-        <v>944</v>
-      </c>
-      <c r="F232" t="inlineStr"/>
+        <v>651</v>
+      </c>
+      <c r="F232" t="n">
+        <v>7884.98</v>
+      </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H232" t="n">
-        <v>54.7</v>
+        <v>56.9</v>
       </c>
       <c r="I232" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>BG42</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C233" t="n">
-        <v>3871691</v>
+        <v>3225013</v>
       </c>
       <c r="D233" t="n">
-        <v>2158726</v>
+        <v>519839</v>
       </c>
       <c r="E233" t="n">
-        <v>295</v>
+        <v>894</v>
       </c>
       <c r="F233" t="n">
-        <v>14620.19</v>
+        <v>0</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="H233" t="n">
-        <v>54.7</v>
+        <v>56.9</v>
       </c>
       <c r="I233" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C234" t="n">
-        <v>1781185</v>
+        <v>11596941</v>
       </c>
       <c r="D234" t="n">
-        <v>89341</v>
+        <v>8779633</v>
       </c>
       <c r="E234" t="n">
-        <v>794</v>
+        <v>1229</v>
       </c>
       <c r="F234" t="n">
-        <v>596.87</v>
+        <v>31599.5</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H234" t="n">
-        <v>54.7</v>
+        <v>83</v>
       </c>
       <c r="I234" t="n">
-        <v>49</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>EL41</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C235" t="n">
-        <v>1640668</v>
+        <v>2178034</v>
       </c>
       <c r="D235" t="n">
-        <v>247845</v>
+        <v>1686031</v>
       </c>
       <c r="E235" t="n">
-        <v>926</v>
+        <v>1007</v>
       </c>
       <c r="F235" t="n">
-        <v>1354.61</v>
+        <v>1565.56</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>54.7</v>
+        <v>83</v>
       </c>
       <c r="I235" t="n">
-        <v>49</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RS11</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C236" t="n">
-        <v>2137233</v>
+        <v>32447938</v>
       </c>
       <c r="D236" t="n">
-        <v>1897158</v>
+        <v>30600629</v>
       </c>
       <c r="E236" t="n">
-        <v>2822</v>
+        <v>6301</v>
       </c>
       <c r="F236" t="n">
-        <v>7949.35</v>
+        <v>15474.38</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="I236" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="I236" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RS12</t>
+          <t>EL43</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C237" t="n">
-        <v>758862</v>
+        <v>28949170</v>
       </c>
       <c r="D237" t="n">
-        <v>420722</v>
+        <v>27567942</v>
       </c>
       <c r="E237" t="n">
-        <v>4167</v>
-      </c>
-      <c r="F237" t="inlineStr"/>
+        <v>4315</v>
+      </c>
+      <c r="F237" t="n">
+        <v>13387.33</v>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H237" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="I237" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="I237" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RS21</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C238" t="n">
-        <v>1809907</v>
+        <v>2406601</v>
       </c>
       <c r="D238" t="n">
-        <v>501702</v>
+        <v>1614990</v>
       </c>
       <c r="E238" t="n">
-        <v>10631</v>
-      </c>
-      <c r="F238" t="inlineStr"/>
+        <v>1303</v>
+      </c>
+      <c r="F238" t="n">
+        <v>594.41</v>
+      </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H238" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="I238" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="I238" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RS22</t>
+          <t>EL52</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C239" t="n">
-        <v>917342</v>
+        <v>11662778</v>
       </c>
       <c r="D239" t="n">
-        <v>317203</v>
+        <v>8922223</v>
       </c>
       <c r="E239" t="n">
-        <v>6622</v>
+        <v>4215</v>
       </c>
       <c r="F239" t="n">
-        <v>448.02</v>
+        <v>7369.81</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="I239" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C240" t="n">
-        <v>2828659</v>
+        <v>297620</v>
       </c>
       <c r="D240" t="n">
-        <v>1540535</v>
+        <v>39527</v>
       </c>
       <c r="E240" t="n">
-        <v>2679</v>
-      </c>
-      <c r="F240" t="inlineStr"/>
+        <v>161</v>
+      </c>
+      <c r="F240" t="n">
+        <v>6.96</v>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H240" t="n">
-        <v>89.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I240" t="n">
-        <v>21</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C241" t="n">
-        <v>5071764</v>
+        <v>1886268</v>
       </c>
       <c r="D241" t="n">
-        <v>4050390</v>
+        <v>828796</v>
       </c>
       <c r="E241" t="n">
-        <v>8181</v>
+        <v>1130</v>
       </c>
       <c r="F241" t="n">
-        <v>1268.35</v>
+        <v>111.05</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H241" t="n">
-        <v>89.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I241" t="n">
-        <v>21</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>AL01</t>
+          <t>EL61</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>2024</v>
       </c>
       <c r="C242" t="n">
-        <v>1529990</v>
+        <v>2696953</v>
       </c>
       <c r="D242" t="n">
-        <v>1028712</v>
+        <v>1441211</v>
       </c>
       <c r="E242" t="n">
-        <v>540</v>
-      </c>
-      <c r="F242" t="inlineStr"/>
+        <v>1558</v>
+      </c>
+      <c r="F242" t="n">
+        <v>624.05</v>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H242" t="n">
-        <v>62.9</v>
+        <v>83</v>
       </c>
       <c r="I242" t="n">
-        <v>113</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>AL02</t>
+          <t>EL62</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>2024</v>
       </c>
       <c r="C243" t="n">
-        <v>2995317</v>
+        <v>14327897</v>
       </c>
       <c r="D243" t="n">
-        <v>2396565</v>
+        <v>13403976</v>
       </c>
       <c r="E243" t="n">
-        <v>589</v>
-      </c>
-      <c r="F243" t="inlineStr"/>
+        <v>4582</v>
+      </c>
+      <c r="F243" t="n">
+        <v>7420.75</v>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H243" t="n">
-        <v>62.9</v>
+        <v>83</v>
       </c>
       <c r="I243" t="n">
-        <v>113</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>AL03</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="B244" t="n">
         <v>2024</v>
       </c>
       <c r="C244" t="n">
-        <v>2385161</v>
+        <v>2077129</v>
       </c>
       <c r="D244" t="n">
-        <v>1445516</v>
+        <v>1123758</v>
       </c>
       <c r="E244" t="n">
-        <v>969</v>
-      </c>
-      <c r="F244" t="inlineStr"/>
+        <v>451</v>
+      </c>
+      <c r="F244" t="n">
+        <v>977.8200000000001</v>
+      </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H244" t="n">
-        <v>62.9</v>
+        <v>83</v>
       </c>
       <c r="I244" t="n">
-        <v>113</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>2024</v>
       </c>
       <c r="C245" t="n">
-        <v>607563</v>
+        <v>2224431</v>
       </c>
       <c r="D245" t="n">
-        <v>81127</v>
+        <v>1016463</v>
       </c>
       <c r="E245" t="n">
-        <v>268</v>
-      </c>
-      <c r="F245" t="inlineStr"/>
+        <v>1156</v>
+      </c>
+      <c r="F245" t="n">
+        <v>18.03</v>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H245" t="n">
-        <v>56.9</v>
+        <v>83</v>
       </c>
       <c r="I245" t="n">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BG32</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>2024</v>
       </c>
       <c r="C246" t="n">
-        <v>643417</v>
+        <v>4126640</v>
       </c>
       <c r="D246" t="n">
-        <v>130122</v>
+        <v>2018211</v>
       </c>
       <c r="E246" t="n">
-        <v>385</v>
-      </c>
-      <c r="F246" t="inlineStr"/>
+        <v>1700</v>
+      </c>
+      <c r="F246" t="n">
+        <v>334.1</v>
+      </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="H246" t="n">
-        <v>56.9</v>
+        <v>83</v>
       </c>
       <c r="I246" t="n">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BG33</t>
+          <t>HR02</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>2024</v>
       </c>
       <c r="C247" t="n">
-        <v>6250742</v>
+        <v>419145</v>
       </c>
       <c r="D247" t="n">
-        <v>4869399</v>
+        <v>213860</v>
       </c>
       <c r="E247" t="n">
-        <v>703</v>
+        <v>2831</v>
       </c>
       <c r="F247" t="n">
-        <v>1534.75</v>
+        <v>0</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H247" t="n">
-        <v>56.9</v>
+        <v>73.3</v>
       </c>
       <c r="I247" t="n">
-        <v>92</v>
+        <v>894</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>HR03</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>2024</v>
       </c>
       <c r="C248" t="n">
-        <v>9875732</v>
+        <v>22784079</v>
       </c>
       <c r="D248" t="n">
-        <v>6802140</v>
+        <v>19841182</v>
       </c>
       <c r="E248" t="n">
-        <v>1148</v>
+        <v>115285</v>
       </c>
       <c r="F248" t="n">
-        <v>1781.24</v>
+        <v>8737.67</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H248" t="n">
-        <v>56.9</v>
+        <v>73.3</v>
       </c>
       <c r="I248" t="n">
-        <v>92</v>
+        <v>894</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BG41</t>
+          <t>HR05</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>2024</v>
       </c>
       <c r="C249" t="n">
-        <v>4754940</v>
+        <v>1695329</v>
       </c>
       <c r="D249" t="n">
-        <v>2348979</v>
+        <v>1379603</v>
       </c>
       <c r="E249" t="n">
-        <v>651</v>
+        <v>2771</v>
       </c>
       <c r="F249" t="n">
-        <v>7884.98</v>
+        <v>0</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H249" t="n">
-        <v>56.9</v>
+        <v>73.3</v>
       </c>
       <c r="I249" t="n">
-        <v>92</v>
+        <v>894</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>BG42</t>
+          <t>HR06</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>2024</v>
       </c>
       <c r="C250" t="n">
-        <v>3225013</v>
+        <v>661879</v>
       </c>
       <c r="D250" t="n">
-        <v>519839</v>
+        <v>352703</v>
       </c>
       <c r="E250" t="n">
+        <v>1551</v>
+      </c>
+      <c r="F250" t="n">
+        <v>4288.55</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="I250" t="n">
         <v>894</v>
-      </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="H250" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I250" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>2024</v>
       </c>
       <c r="C251" t="n">
-        <v>11596941</v>
+        <v>2988614</v>
       </c>
       <c r="D251" t="n">
-        <v>8779633</v>
+        <v>424167</v>
       </c>
       <c r="E251" t="n">
-        <v>1229</v>
+        <v>1869</v>
       </c>
       <c r="F251" t="n">
-        <v>31599.5</v>
+        <v>3434.27</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I251" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>EL41</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>2024</v>
       </c>
       <c r="C252" t="n">
-        <v>2178034</v>
+        <v>4637522</v>
       </c>
       <c r="D252" t="n">
-        <v>1686031</v>
+        <v>720254</v>
       </c>
       <c r="E252" t="n">
-        <v>1007</v>
+        <v>3079</v>
       </c>
       <c r="F252" t="n">
-        <v>1565.56</v>
+        <v>782.6</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I252" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>2024</v>
       </c>
       <c r="C253" t="n">
-        <v>32447938</v>
+        <v>1979723</v>
       </c>
       <c r="D253" t="n">
-        <v>30600629</v>
+        <v>223827</v>
       </c>
       <c r="E253" t="n">
-        <v>6301</v>
+        <v>1461</v>
       </c>
       <c r="F253" t="n">
-        <v>15474.38</v>
+        <v>3501.86</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I253" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>EL43</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>2024</v>
       </c>
       <c r="C254" t="n">
-        <v>28949170</v>
+        <v>6118170</v>
       </c>
       <c r="D254" t="n">
-        <v>27567942</v>
+        <v>221369</v>
       </c>
       <c r="E254" t="n">
-        <v>4315</v>
+        <v>2687</v>
       </c>
       <c r="F254" t="n">
-        <v>13387.33</v>
+        <v>0</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I254" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>EL51</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>2024</v>
       </c>
       <c r="C255" t="n">
-        <v>2406601</v>
+        <v>1894672</v>
       </c>
       <c r="D255" t="n">
-        <v>1614990</v>
+        <v>239255</v>
       </c>
       <c r="E255" t="n">
-        <v>1303</v>
+        <v>998</v>
       </c>
       <c r="F255" t="n">
-        <v>594.41</v>
+        <v>0</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I255" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EL52</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>2024</v>
       </c>
       <c r="C256" t="n">
-        <v>11662778</v>
+        <v>4192942</v>
       </c>
       <c r="D256" t="n">
-        <v>8922223</v>
+        <v>2474464</v>
       </c>
       <c r="E256" t="n">
-        <v>4215</v>
+        <v>332</v>
       </c>
       <c r="F256" t="n">
-        <v>7369.81</v>
+        <v>15939.88</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I256" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>2024</v>
       </c>
       <c r="C257" t="n">
-        <v>297620</v>
+        <v>1899909</v>
       </c>
       <c r="D257" t="n">
-        <v>39527</v>
+        <v>87705</v>
       </c>
       <c r="E257" t="n">
-        <v>161</v>
+        <v>793</v>
       </c>
       <c r="F257" t="n">
-        <v>6.96</v>
+        <v>424</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I257" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>EL54</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="B258" t="n">
         <v>2024</v>
       </c>
       <c r="C258" t="n">
-        <v>1886268</v>
+        <v>1671218</v>
       </c>
       <c r="D258" t="n">
-        <v>828796</v>
+        <v>256927</v>
       </c>
       <c r="E258" t="n">
-        <v>1130</v>
+        <v>1004</v>
       </c>
       <c r="F258" t="n">
-        <v>111.05</v>
+        <v>1323.45</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>83</v>
+        <v>57.4</v>
       </c>
       <c r="I258" t="n">
-        <v>1728</v>
+        <v>49</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EL61</t>
+          <t>RS11</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>2024</v>
       </c>
       <c r="C259" t="n">
-        <v>2696953</v>
+        <v>2228063</v>
       </c>
       <c r="D259" t="n">
-        <v>1441211</v>
+        <v>2016136</v>
       </c>
       <c r="E259" t="n">
-        <v>1558</v>
+        <v>3345</v>
       </c>
       <c r="F259" t="n">
-        <v>624.05</v>
+        <v>8367.4</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>83</v>
+        <v>61.4</v>
       </c>
       <c r="I259" t="n">
-        <v>1728</v>
+        <v>58</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>EL62</t>
+          <t>RS12</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>2024</v>
       </c>
       <c r="C260" t="n">
-        <v>14327897</v>
+        <v>770107</v>
       </c>
       <c r="D260" t="n">
-        <v>13403976</v>
+        <v>464938</v>
       </c>
       <c r="E260" t="n">
-        <v>4582</v>
+        <v>4740</v>
       </c>
       <c r="F260" t="n">
-        <v>7420.75</v>
+        <v>0</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>83</v>
+        <v>61.4</v>
       </c>
       <c r="I260" t="n">
-        <v>1728</v>
+        <v>58</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>RS21</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>2024</v>
       </c>
       <c r="C261" t="n">
-        <v>2077129</v>
+        <v>1929905</v>
       </c>
       <c r="D261" t="n">
-        <v>1123758</v>
+        <v>580591</v>
       </c>
       <c r="E261" t="n">
-        <v>451</v>
+        <v>12100</v>
       </c>
       <c r="F261" t="n">
-        <v>977.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>83</v>
+        <v>61.4</v>
       </c>
       <c r="I261" t="n">
-        <v>1728</v>
+        <v>58</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>RS22</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>2024</v>
       </c>
       <c r="C262" t="n">
-        <v>2224431</v>
+        <v>999948</v>
       </c>
       <c r="D262" t="n">
-        <v>1016463</v>
+        <v>339565</v>
       </c>
       <c r="E262" t="n">
-        <v>1156</v>
+        <v>7001</v>
       </c>
       <c r="F262" t="n">
-        <v>18.03</v>
+        <v>357.31</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>83</v>
+        <v>61.4</v>
       </c>
       <c r="I262" t="n">
-        <v>1728</v>
+        <v>58</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>2024</v>
       </c>
       <c r="C263" t="n">
-        <v>4126640</v>
+        <v>2916662</v>
       </c>
       <c r="D263" t="n">
-        <v>2018211</v>
+        <v>1611316</v>
       </c>
       <c r="E263" t="n">
-        <v>1700</v>
+        <v>2850</v>
       </c>
       <c r="F263" t="n">
-        <v>334.1</v>
+        <v>0</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I263" t="n">
-        <v>1728</v>
+        <v>21</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HR02</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>2024</v>
       </c>
       <c r="C264" t="n">
-        <v>419145</v>
+        <v>5405705</v>
       </c>
       <c r="D264" t="n">
-        <v>213860</v>
+        <v>4441927</v>
       </c>
       <c r="E264" t="n">
-        <v>2831</v>
-      </c>
-      <c r="F264" t="inlineStr"/>
+        <v>8762</v>
+      </c>
+      <c r="F264" t="n">
+        <v>1437.66</v>
+      </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>73.3</v>
+        <v>91</v>
       </c>
       <c r="I264" t="n">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>HR03</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C265" t="n">
-        <v>22784079</v>
-      </c>
-      <c r="D265" t="n">
-        <v>19841182</v>
-      </c>
-      <c r="E265" t="n">
-        <v>115285</v>
-      </c>
-      <c r="F265" t="n">
-        <v>8737.67</v>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="H265" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="I265" t="n">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>HR05</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C266" t="n">
-        <v>1695329</v>
-      </c>
-      <c r="D266" t="n">
-        <v>1379603</v>
-      </c>
-      <c r="E266" t="n">
-        <v>2771</v>
-      </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="H266" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="I266" t="n">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>HR06</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C267" t="n">
-        <v>661879</v>
-      </c>
-      <c r="D267" t="n">
-        <v>352703</v>
-      </c>
-      <c r="E267" t="n">
-        <v>1551</v>
-      </c>
-      <c r="F267" t="n">
-        <v>4288.55</v>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="H267" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="I267" t="n">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>ME00</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C268" t="n">
-        <v>4849183</v>
-      </c>
-      <c r="D268" t="n">
-        <v>4425995</v>
-      </c>
-      <c r="E268" t="n">
-        <v>459</v>
-      </c>
-      <c r="F268" t="n">
-        <v>2871.77</v>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="H268" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="I268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>MK00</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C269" t="n">
-        <v>1968935</v>
-      </c>
-      <c r="D269" t="n">
-        <v>1486164</v>
-      </c>
-      <c r="E269" t="n">
-        <v>509</v>
-      </c>
-      <c r="F269" t="n">
-        <v>3169.42</v>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="H269" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="I269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>RO11</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C270" t="n">
-        <v>2988614</v>
-      </c>
-      <c r="D270" t="n">
-        <v>424167</v>
-      </c>
-      <c r="E270" t="n">
-        <v>1869</v>
-      </c>
-      <c r="F270" t="n">
-        <v>3434.27</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H270" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I270" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>RO12</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C271" t="n">
-        <v>4637522</v>
-      </c>
-      <c r="D271" t="n">
-        <v>720254</v>
-      </c>
-      <c r="E271" t="n">
-        <v>3079</v>
-      </c>
-      <c r="F271" t="n">
-        <v>782.6</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H271" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I271" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>RO21</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C272" t="n">
-        <v>1979723</v>
-      </c>
-      <c r="D272" t="n">
-        <v>223827</v>
-      </c>
-      <c r="E272" t="n">
-        <v>1461</v>
-      </c>
-      <c r="F272" t="n">
-        <v>3501.86</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I272" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>RO22</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C273" t="n">
-        <v>6118170</v>
-      </c>
-      <c r="D273" t="n">
-        <v>221369</v>
-      </c>
-      <c r="E273" t="n">
-        <v>2687</v>
-      </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I273" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>RO31</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C274" t="n">
-        <v>1894672</v>
-      </c>
-      <c r="D274" t="n">
-        <v>239255</v>
-      </c>
-      <c r="E274" t="n">
-        <v>998</v>
-      </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I274" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>RO32</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C275" t="n">
-        <v>4192942</v>
-      </c>
-      <c r="D275" t="n">
-        <v>2474464</v>
-      </c>
-      <c r="E275" t="n">
-        <v>332</v>
-      </c>
-      <c r="F275" t="n">
-        <v>15939.88</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I275" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>RO41</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C276" t="n">
-        <v>1899909</v>
-      </c>
-      <c r="D276" t="n">
-        <v>87705</v>
-      </c>
-      <c r="E276" t="n">
-        <v>793</v>
-      </c>
-      <c r="F276" t="n">
-        <v>424</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I276" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>RO42</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C277" t="n">
-        <v>1671218</v>
-      </c>
-      <c r="D277" t="n">
-        <v>256927</v>
-      </c>
-      <c r="E277" t="n">
-        <v>1004</v>
-      </c>
-      <c r="F277" t="n">
-        <v>1323.45</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I277" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>RS11</t>
-        </is>
-      </c>
-      <c r="B278" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C278" t="n">
-        <v>2228063</v>
-      </c>
-      <c r="D278" t="n">
-        <v>2016136</v>
-      </c>
-      <c r="E278" t="n">
-        <v>3345</v>
-      </c>
-      <c r="F278" t="n">
-        <v>8367.4</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>RS12</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C279" t="n">
-        <v>770107</v>
-      </c>
-      <c r="D279" t="n">
-        <v>464938</v>
-      </c>
-      <c r="E279" t="n">
-        <v>4740</v>
-      </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>RS21</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C280" t="n">
-        <v>1929905</v>
-      </c>
-      <c r="D280" t="n">
-        <v>580591</v>
-      </c>
-      <c r="E280" t="n">
-        <v>12100</v>
-      </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>RS22</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C281" t="n">
-        <v>999948</v>
-      </c>
-      <c r="D281" t="n">
-        <v>339565</v>
-      </c>
-      <c r="E281" t="n">
-        <v>7001</v>
-      </c>
-      <c r="F281" t="n">
-        <v>357.31</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>SI03</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C282" t="n">
-        <v>2916662</v>
-      </c>
-      <c r="D282" t="n">
-        <v>1611316</v>
-      </c>
-      <c r="E282" t="n">
-        <v>2850</v>
-      </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H282" t="n">
-        <v>91</v>
-      </c>
-      <c r="I282" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>SI04</t>
-        </is>
-      </c>
-      <c r="B283" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C283" t="n">
-        <v>5405705</v>
-      </c>
-      <c r="D283" t="n">
-        <v>4441927</v>
-      </c>
-      <c r="E283" t="n">
-        <v>8762</v>
-      </c>
-      <c r="F283" t="n">
-        <v>1437.66</v>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H283" t="n">
-        <v>91</v>
-      </c>
-      <c r="I283" t="n">
         <v>21</v>
       </c>
     </row>
